--- a/research/traditional_assets/database/data/denmark/denmark_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_computers_peripherals.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ob_astk" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00368</v>
+        <v>0.00133</v>
+      </c>
+      <c r="E2">
+        <v>-0.0481</v>
       </c>
       <c r="G2">
-        <v>0.1510961214165261</v>
+        <v>0.0384393063583815</v>
       </c>
       <c r="H2">
-        <v>0.06155143338954469</v>
+        <v>-0.05317919075144509</v>
       </c>
       <c r="I2">
-        <v>-0.07993254637436763</v>
+        <v>0.1049132947976879</v>
       </c>
       <c r="J2">
-        <v>-0.07993254637436763</v>
+        <v>0.1049132947976879</v>
       </c>
       <c r="K2">
-        <v>-2.65</v>
+        <v>4.99</v>
       </c>
       <c r="L2">
-        <v>-0.04468802698145025</v>
+        <v>0.07210982658959537</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>11</v>
+        <v>7.33</v>
       </c>
       <c r="V2">
-        <v>0.3503184713375797</v>
+        <v>0.1320720720720721</v>
       </c>
       <c r="W2">
-        <v>-0.05463917525773196</v>
+        <v>0.116046511627907</v>
       </c>
       <c r="X2">
-        <v>0.1142413756674952</v>
+        <v>0.1081685528445649</v>
       </c>
       <c r="Y2">
-        <v>-0.1688805509252272</v>
+        <v>0.007877958783342062</v>
       </c>
       <c r="Z2">
-        <v>2.258187357197258</v>
+        <v>2.049156055670713</v>
       </c>
       <c r="AA2">
-        <v>-0.1805026656511805</v>
+        <v>0.2149837133550488</v>
       </c>
       <c r="AB2">
-        <v>0.1104344949038092</v>
+        <v>0.09763254424536012</v>
       </c>
       <c r="AC2">
-        <v>-0.2909371605549897</v>
+        <v>0.1173511691096887</v>
       </c>
       <c r="AD2">
-        <v>1.77</v>
+        <v>14.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.77</v>
+        <v>14.9</v>
       </c>
       <c r="AG2">
-        <v>-9.23</v>
+        <v>7.57</v>
       </c>
       <c r="AH2">
-        <v>0.05336147120892373</v>
+        <v>0.2116477272727273</v>
       </c>
       <c r="AI2">
-        <v>0.03953540317176681</v>
+        <v>0.1850931677018633</v>
       </c>
       <c r="AJ2">
-        <v>-0.4163283716734326</v>
+        <v>0.1200253686380213</v>
       </c>
       <c r="AK2">
-        <v>-0.2733195143618597</v>
+        <v>0.1034577012436791</v>
       </c>
       <c r="AL2">
-        <v>0.053</v>
+        <v>0.008</v>
       </c>
       <c r="AM2">
-        <v>0.051</v>
+        <v>-0.132</v>
       </c>
       <c r="AN2">
-        <v>-0.7468354430379747</v>
+        <v>1.578389830508475</v>
       </c>
       <c r="AO2">
-        <v>-89.43396226415095</v>
+        <v>907.5</v>
       </c>
       <c r="AP2">
-        <v>3.89451476793249</v>
+        <v>0.801906779661017</v>
       </c>
       <c r="AQ2">
-        <v>-92.94117647058825</v>
+        <v>-54.99999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00368</v>
+        <v>0.00133</v>
+      </c>
+      <c r="E3">
+        <v>-0.0481</v>
       </c>
       <c r="G3">
-        <v>0.1510961214165261</v>
+        <v>0.0384393063583815</v>
       </c>
       <c r="H3">
-        <v>0.06155143338954469</v>
+        <v>-0.05317919075144509</v>
       </c>
       <c r="I3">
-        <v>-0.07993254637436763</v>
+        <v>0.1049132947976879</v>
       </c>
       <c r="J3">
-        <v>-0.07993254637436763</v>
+        <v>0.1049132947976879</v>
       </c>
       <c r="K3">
-        <v>-2.65</v>
+        <v>4.99</v>
       </c>
       <c r="L3">
-        <v>-0.04468802698145025</v>
+        <v>0.07210982658959537</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8851 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>11</v>
+        <v>7.33</v>
       </c>
       <c r="V3">
-        <v>0.3503184713375797</v>
+        <v>0.1320720720720721</v>
       </c>
       <c r="W3">
-        <v>-0.05463917525773196</v>
+        <v>0.116046511627907</v>
       </c>
       <c r="X3">
-        <v>0.1142413756674952</v>
+        <v>0.1081685528445649</v>
       </c>
       <c r="Y3">
-        <v>-0.1688805509252272</v>
+        <v>0.007877958783342062</v>
       </c>
       <c r="Z3">
-        <v>2.258187357197258</v>
+        <v>2.049156055670713</v>
       </c>
       <c r="AA3">
-        <v>-0.1805026656511805</v>
+        <v>0.2149837133550488</v>
       </c>
       <c r="AB3">
-        <v>0.1104344949038092</v>
+        <v>0.09763254424536012</v>
       </c>
       <c r="AC3">
-        <v>-0.2909371605549897</v>
+        <v>0.1173511691096887</v>
       </c>
       <c r="AD3">
-        <v>1.77</v>
+        <v>14.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.77</v>
+        <v>14.9</v>
       </c>
       <c r="AG3">
-        <v>-9.23</v>
+        <v>7.57</v>
       </c>
       <c r="AH3">
-        <v>0.05336147120892373</v>
+        <v>0.2116477272727273</v>
       </c>
       <c r="AI3">
-        <v>0.03953540317176681</v>
+        <v>0.1850931677018633</v>
       </c>
       <c r="AJ3">
-        <v>-0.4163283716734326</v>
+        <v>0.1200253686380213</v>
       </c>
       <c r="AK3">
-        <v>-0.2733195143618597</v>
+        <v>0.1034577012436791</v>
       </c>
       <c r="AL3">
-        <v>0.053</v>
+        <v>0.008</v>
       </c>
       <c r="AM3">
-        <v>0.051</v>
+        <v>-0.132</v>
       </c>
       <c r="AN3">
-        <v>-0.7468354430379747</v>
+        <v>1.578389830508475</v>
       </c>
       <c r="AO3">
-        <v>-89.43396226415095</v>
+        <v>907.5</v>
       </c>
       <c r="AP3">
-        <v>3.89451476793249</v>
+        <v>0.801906779661017</v>
       </c>
       <c r="AQ3">
-        <v>-92.94117647058825</v>
+        <v>-54.99999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Asetek A/S (OB:ASTK)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OB:ASTK</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Computers/Peripherals</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>907.5</v>
+      </c>
+      <c r="F2">
+        <v>4.50229207596595</v>
+      </c>
+      <c r="G2">
+        <v>1.57838983050847</v>
+      </c>
+      <c r="H2">
+        <v>3.35593220338983</v>
+      </c>
+      <c r="I2">
+        <v>0.211647727272727</v>
+      </c>
+      <c r="J2">
+        <v>0.45</v>
+      </c>
+      <c r="K2">
+        <v>55.5</v>
+      </c>
+      <c r="L2">
+        <v>46.8905426334695</v>
+      </c>
+      <c r="M2">
+        <v>63.07</v>
+      </c>
+      <c r="N2">
+        <v>71.2405426334695</v>
+      </c>
+      <c r="O2">
+        <v>14.9</v>
+      </c>
+      <c r="P2">
+        <v>31.68</v>
+      </c>
+      <c r="Q2">
+        <v>0.0976325442453601</v>
+      </c>
+      <c r="R2">
+        <v>0.09088506881602</v>
+      </c>
+      <c r="S2">
+        <v>0.05838768</v>
+      </c>
+      <c r="T2">
+        <v>0.039702</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.108168552844565</v>
+      </c>
+      <c r="X2">
+        <v>0.132762125120036</v>
+      </c>
+      <c r="Y2">
+        <v>1.50801201836011</v>
+      </c>
+      <c r="Z2">
+        <v>2.04265489391383</v>
+      </c>
+      <c r="AA2">
+        <v>14.9</v>
+      </c>
+      <c r="AB2">
+        <v>0.07485600000000001</v>
+      </c>
+      <c r="AC2">
+        <v>907.5</v>
+      </c>
+      <c r="AD2">
+        <v>14.9</v>
+      </c>
+      <c r="AE2">
+        <v>0.008</v>
+      </c>
+      <c r="AF2">
+        <v>2.18</v>
+      </c>
+      <c r="AG2">
+        <v>9.44</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>55.5</v>
+      </c>
+      <c r="AK2">
+        <v>0.046</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.22</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>24.38</v>
+      </c>
+      <c r="AR2">
+        <v>0.008</v>
+      </c>
+      <c r="AS2">
+        <v>14.9</v>
+      </c>
+      <c r="AT2">
+        <v>7.33</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09615756805329628</v>
+      </c>
+      <c r="C2">
+        <v>72.02187400182356</v>
+      </c>
+      <c r="D2">
+        <v>64.69187400182356</v>
+      </c>
+      <c r="E2">
+        <v>-14.9</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>7.33</v>
+      </c>
+      <c r="H2">
+        <v>55.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>9.44</v>
+      </c>
+      <c r="K2">
+        <v>2.18</v>
+      </c>
+      <c r="L2">
+        <v>7.26</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>7.26</v>
+      </c>
+      <c r="O2">
+        <v>1.5972</v>
+      </c>
+      <c r="P2">
+        <v>5.6628</v>
+      </c>
+      <c r="Q2">
+        <v>7.8428</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09615756805329628</v>
+      </c>
+      <c r="T2">
+        <v>1.246903653332528</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.22</v>
+      </c>
+      <c r="W2">
+        <v>0.034866</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09599204140357905</v>
+      </c>
+      <c r="C3">
+        <v>71.50510685633715</v>
+      </c>
+      <c r="D3">
+        <v>64.87910685633715</v>
+      </c>
+      <c r="E3">
+        <v>-14.196</v>
+      </c>
+      <c r="F3">
+        <v>0.7040000000000001</v>
+      </c>
+      <c r="G3">
+        <v>7.33</v>
+      </c>
+      <c r="H3">
+        <v>55.5</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>9.44</v>
+      </c>
+      <c r="K3">
+        <v>2.18</v>
+      </c>
+      <c r="L3">
+        <v>7.26</v>
+      </c>
+      <c r="M3">
+        <v>0.03146880000000001</v>
+      </c>
+      <c r="N3">
+        <v>7.2285312</v>
+      </c>
+      <c r="O3">
+        <v>1.590276864</v>
+      </c>
+      <c r="P3">
+        <v>5.638254336</v>
+      </c>
+      <c r="Q3">
+        <v>7.818254336</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09660947616523136</v>
+      </c>
+      <c r="T3">
+        <v>1.256727742722421</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.22</v>
+      </c>
+      <c r="W3">
+        <v>0.034866</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>230.7046979865771</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09582651475386178</v>
+      </c>
+      <c r="C4">
+        <v>70.98942664478872</v>
+      </c>
+      <c r="D4">
+        <v>65.06742664478872</v>
+      </c>
+      <c r="E4">
+        <v>-13.492</v>
+      </c>
+      <c r="F4">
+        <v>1.408</v>
+      </c>
+      <c r="G4">
+        <v>7.33</v>
+      </c>
+      <c r="H4">
+        <v>55.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>9.44</v>
+      </c>
+      <c r="K4">
+        <v>2.18</v>
+      </c>
+      <c r="L4">
+        <v>7.26</v>
+      </c>
+      <c r="M4">
+        <v>0.06293760000000001</v>
+      </c>
+      <c r="N4">
+        <v>7.1970624</v>
+      </c>
+      <c r="O4">
+        <v>1.583353728</v>
+      </c>
+      <c r="P4">
+        <v>5.613708672</v>
+      </c>
+      <c r="Q4">
+        <v>7.793708671999999</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09707060689169569</v>
+      </c>
+      <c r="T4">
+        <v>1.266752323732515</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.22</v>
+      </c>
+      <c r="W4">
+        <v>0.034866</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>115.3523489932886</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09566098810414453</v>
+      </c>
+      <c r="C5">
+        <v>70.47484285961968</v>
+      </c>
+      <c r="D5">
+        <v>65.25684285961968</v>
+      </c>
+      <c r="E5">
+        <v>-12.788</v>
+      </c>
+      <c r="F5">
+        <v>2.112</v>
+      </c>
+      <c r="G5">
+        <v>7.33</v>
+      </c>
+      <c r="H5">
+        <v>55.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>9.44</v>
+      </c>
+      <c r="K5">
+        <v>2.18</v>
+      </c>
+      <c r="L5">
+        <v>7.26</v>
+      </c>
+      <c r="M5">
+        <v>0.09440640000000002</v>
+      </c>
+      <c r="N5">
+        <v>7.165593599999999</v>
+      </c>
+      <c r="O5">
+        <v>1.576430592</v>
+      </c>
+      <c r="P5">
+        <v>5.589163008</v>
+      </c>
+      <c r="Q5">
+        <v>7.769163008</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09754124546819024</v>
+      </c>
+      <c r="T5">
+        <v>1.27698359713457</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.22</v>
+      </c>
+      <c r="W5">
+        <v>0.034866</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>76.9015659955257</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09549546145442728</v>
+      </c>
+      <c r="C6">
+        <v>69.96136510412704</v>
+      </c>
+      <c r="D6">
+        <v>65.44736510412704</v>
+      </c>
+      <c r="E6">
+        <v>-12.084</v>
+      </c>
+      <c r="F6">
+        <v>2.816</v>
+      </c>
+      <c r="G6">
+        <v>7.33</v>
+      </c>
+      <c r="H6">
+        <v>55.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>9.44</v>
+      </c>
+      <c r="K6">
+        <v>2.18</v>
+      </c>
+      <c r="L6">
+        <v>7.26</v>
+      </c>
+      <c r="M6">
+        <v>0.1258752</v>
+      </c>
+      <c r="N6">
+        <v>7.134124799999999</v>
+      </c>
+      <c r="O6">
+        <v>1.569507456</v>
+      </c>
+      <c r="P6">
+        <v>5.564617343999999</v>
+      </c>
+      <c r="Q6">
+        <v>7.744617343999999</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09802168901502842</v>
+      </c>
+      <c r="T6">
+        <v>1.287428022065835</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.22</v>
+      </c>
+      <c r="W6">
+        <v>0.034866</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>57.67617449664428</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09532993480471003</v>
+      </c>
+      <c r="C7">
+        <v>69.44900309408639</v>
+      </c>
+      <c r="D7">
+        <v>65.63900309408639</v>
+      </c>
+      <c r="E7">
+        <v>-11.38</v>
+      </c>
+      <c r="F7">
+        <v>3.52</v>
+      </c>
+      <c r="G7">
+        <v>7.33</v>
+      </c>
+      <c r="H7">
+        <v>55.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>9.44</v>
+      </c>
+      <c r="K7">
+        <v>2.18</v>
+      </c>
+      <c r="L7">
+        <v>7.26</v>
+      </c>
+      <c r="M7">
+        <v>0.157344</v>
+      </c>
+      <c r="N7">
+        <v>7.102656</v>
+      </c>
+      <c r="O7">
+        <v>1.56258432</v>
+      </c>
+      <c r="P7">
+        <v>5.54007168</v>
+      </c>
+      <c r="Q7">
+        <v>7.720071679999999</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09851224716285266</v>
+      </c>
+      <c r="T7">
+        <v>1.298092329627232</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.22</v>
+      </c>
+      <c r="W7">
+        <v>0.034866</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>46.14093959731542</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09516440815499277</v>
+      </c>
+      <c r="C8">
+        <v>68.93776665940348</v>
+      </c>
+      <c r="D8">
+        <v>65.83176665940348</v>
+      </c>
+      <c r="E8">
+        <v>-10.676</v>
+      </c>
+      <c r="F8">
+        <v>4.224</v>
+      </c>
+      <c r="G8">
+        <v>7.33</v>
+      </c>
+      <c r="H8">
+        <v>55.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>9.44</v>
+      </c>
+      <c r="K8">
+        <v>2.18</v>
+      </c>
+      <c r="L8">
+        <v>7.26</v>
+      </c>
+      <c r="M8">
+        <v>0.1888128</v>
+      </c>
+      <c r="N8">
+        <v>7.0711872</v>
+      </c>
+      <c r="O8">
+        <v>1.555661184</v>
+      </c>
+      <c r="P8">
+        <v>5.515526016</v>
+      </c>
+      <c r="Q8">
+        <v>7.695526016</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09901324271807742</v>
+      </c>
+      <c r="T8">
+        <v>1.308983537349509</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.22</v>
+      </c>
+      <c r="W8">
+        <v>0.034866</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>38.45078299776286</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09499888150527554</v>
+      </c>
+      <c r="C9">
+        <v>68.42766574579501</v>
+      </c>
+      <c r="D9">
+        <v>66.02566574579501</v>
+      </c>
+      <c r="E9">
+        <v>-9.972</v>
+      </c>
+      <c r="F9">
+        <v>4.928000000000001</v>
+      </c>
+      <c r="G9">
+        <v>7.33</v>
+      </c>
+      <c r="H9">
+        <v>55.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>9.44</v>
+      </c>
+      <c r="K9">
+        <v>2.18</v>
+      </c>
+      <c r="L9">
+        <v>7.26</v>
+      </c>
+      <c r="M9">
+        <v>0.2202816</v>
+      </c>
+      <c r="N9">
+        <v>7.0397184</v>
+      </c>
+      <c r="O9">
+        <v>1.548738048</v>
+      </c>
+      <c r="P9">
+        <v>5.490980352</v>
+      </c>
+      <c r="Q9">
+        <v>7.670980352</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09952501237126402</v>
+      </c>
+      <c r="T9">
+        <v>1.320108964592696</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.22</v>
+      </c>
+      <c r="W9">
+        <v>0.034866</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>32.95781399808244</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09483335485555827</v>
+      </c>
+      <c r="C10">
+        <v>67.9187104164992</v>
+      </c>
+      <c r="D10">
+        <v>66.2207104164992</v>
+      </c>
+      <c r="E10">
+        <v>-9.268000000000001</v>
+      </c>
+      <c r="F10">
+        <v>5.632000000000001</v>
+      </c>
+      <c r="G10">
+        <v>7.33</v>
+      </c>
+      <c r="H10">
+        <v>55.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>9.44</v>
+      </c>
+      <c r="K10">
+        <v>2.18</v>
+      </c>
+      <c r="L10">
+        <v>7.26</v>
+      </c>
+      <c r="M10">
+        <v>0.2517504</v>
+      </c>
+      <c r="N10">
+        <v>7.0082496</v>
+      </c>
+      <c r="O10">
+        <v>1.541814912</v>
+      </c>
+      <c r="P10">
+        <v>5.466434688</v>
+      </c>
+      <c r="Q10">
+        <v>7.646434687999999</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1000479074516938</v>
+      </c>
+      <c r="T10">
+        <v>1.331476248949865</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.22</v>
+      </c>
+      <c r="W10">
+        <v>0.034866</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>28.83808724832214</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09466782820584102</v>
+      </c>
+      <c r="C11">
+        <v>67.41091085401671</v>
+      </c>
+      <c r="D11">
+        <v>66.41691085401671</v>
+      </c>
+      <c r="E11">
+        <v>-8.564</v>
+      </c>
+      <c r="F11">
+        <v>6.336</v>
+      </c>
+      <c r="G11">
+        <v>7.33</v>
+      </c>
+      <c r="H11">
+        <v>55.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>9.44</v>
+      </c>
+      <c r="K11">
+        <v>2.18</v>
+      </c>
+      <c r="L11">
+        <v>7.26</v>
+      </c>
+      <c r="M11">
+        <v>0.2832192000000001</v>
+      </c>
+      <c r="N11">
+        <v>6.976780799999999</v>
+      </c>
+      <c r="O11">
+        <v>1.534891776</v>
+      </c>
+      <c r="P11">
+        <v>5.441889024</v>
+      </c>
+      <c r="Q11">
+        <v>7.621889024</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1005822947316934</v>
+      </c>
+      <c r="T11">
+        <v>1.343093363732466</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.22</v>
+      </c>
+      <c r="W11">
+        <v>0.034866</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>25.6338553318419</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.09450230155612378</v>
+      </c>
+      <c r="C12">
+        <v>66.90427736188276</v>
+      </c>
+      <c r="D12">
+        <v>66.61427736188277</v>
+      </c>
+      <c r="E12">
+        <v>-7.859999999999999</v>
+      </c>
+      <c r="F12">
+        <v>7.040000000000001</v>
+      </c>
+      <c r="G12">
+        <v>7.33</v>
+      </c>
+      <c r="H12">
+        <v>55.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>9.44</v>
+      </c>
+      <c r="K12">
+        <v>2.18</v>
+      </c>
+      <c r="L12">
+        <v>7.26</v>
+      </c>
+      <c r="M12">
+        <v>0.3146880000000001</v>
+      </c>
+      <c r="N12">
+        <v>6.945311999999999</v>
+      </c>
+      <c r="O12">
+        <v>1.52796864</v>
+      </c>
+      <c r="P12">
+        <v>5.417343359999999</v>
+      </c>
+      <c r="Q12">
+        <v>7.597343359999999</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.101128557284582</v>
+      </c>
+      <c r="T12">
+        <v>1.354968636621347</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.22</v>
+      </c>
+      <c r="W12">
+        <v>0.034866</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>23.07046979865771</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.09433677490640652</v>
+      </c>
+      <c r="C13">
+        <v>66.39882036647083</v>
+      </c>
+      <c r="D13">
+        <v>66.81282036647083</v>
+      </c>
+      <c r="E13">
+        <v>-7.156</v>
+      </c>
+      <c r="F13">
+        <v>7.744000000000001</v>
+      </c>
+      <c r="G13">
+        <v>7.33</v>
+      </c>
+      <c r="H13">
+        <v>55.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>9.44</v>
+      </c>
+      <c r="K13">
+        <v>2.18</v>
+      </c>
+      <c r="L13">
+        <v>7.26</v>
+      </c>
+      <c r="M13">
+        <v>0.3461568</v>
+      </c>
+      <c r="N13">
+        <v>6.9138432</v>
+      </c>
+      <c r="O13">
+        <v>1.521045504</v>
+      </c>
+      <c r="P13">
+        <v>5.392797696</v>
+      </c>
+      <c r="Q13">
+        <v>7.572797695999999</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1016870954004568</v>
+      </c>
+      <c r="T13">
+        <v>1.367110769575147</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.22</v>
+      </c>
+      <c r="W13">
+        <v>0.034866</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>20.9731543624161</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09417124825668925</v>
+      </c>
+      <c r="C14">
+        <v>65.89455041882857</v>
+      </c>
+      <c r="D14">
+        <v>67.01255041882858</v>
+      </c>
+      <c r="E14">
+        <v>-6.452</v>
+      </c>
+      <c r="F14">
+        <v>8.448</v>
+      </c>
+      <c r="G14">
+        <v>7.33</v>
+      </c>
+      <c r="H14">
+        <v>55.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>9.44</v>
+      </c>
+      <c r="K14">
+        <v>2.18</v>
+      </c>
+      <c r="L14">
+        <v>7.26</v>
+      </c>
+      <c r="M14">
+        <v>0.3776256000000001</v>
+      </c>
+      <c r="N14">
+        <v>6.8823744</v>
+      </c>
+      <c r="O14">
+        <v>1.514122368</v>
+      </c>
+      <c r="P14">
+        <v>5.368252032</v>
+      </c>
+      <c r="Q14">
+        <v>7.548252032</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1022583275644196</v>
+      </c>
+      <c r="T14">
+        <v>1.379528860096079</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.22</v>
+      </c>
+      <c r="W14">
+        <v>0.034866</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>19.22539149888143</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09400572160697201</v>
+      </c>
+      <c r="C15">
+        <v>65.39147819654711</v>
+      </c>
+      <c r="D15">
+        <v>67.21347819654711</v>
+      </c>
+      <c r="E15">
+        <v>-5.747999999999999</v>
+      </c>
+      <c r="F15">
+        <v>9.152000000000001</v>
+      </c>
+      <c r="G15">
+        <v>7.33</v>
+      </c>
+      <c r="H15">
+        <v>55.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>9.44</v>
+      </c>
+      <c r="K15">
+        <v>2.18</v>
+      </c>
+      <c r="L15">
+        <v>7.26</v>
+      </c>
+      <c r="M15">
+        <v>0.4090944000000001</v>
+      </c>
+      <c r="N15">
+        <v>6.8509056</v>
+      </c>
+      <c r="O15">
+        <v>1.507199232</v>
+      </c>
+      <c r="P15">
+        <v>5.343706367999999</v>
+      </c>
+      <c r="Q15">
+        <v>7.523706367999999</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1028426915022667</v>
+      </c>
+      <c r="T15">
+        <v>1.392232423962319</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.22</v>
+      </c>
+      <c r="W15">
+        <v>0.034866</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>17.7465152297367</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09384019495725476</v>
+      </c>
+      <c r="C16">
+        <v>64.88961450566373</v>
+      </c>
+      <c r="D16">
+        <v>67.41561450566373</v>
+      </c>
+      <c r="E16">
+        <v>-5.043999999999999</v>
+      </c>
+      <c r="F16">
+        <v>9.856000000000002</v>
+      </c>
+      <c r="G16">
+        <v>7.33</v>
+      </c>
+      <c r="H16">
+        <v>55.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>9.44</v>
+      </c>
+      <c r="K16">
+        <v>2.18</v>
+      </c>
+      <c r="L16">
+        <v>7.26</v>
+      </c>
+      <c r="M16">
+        <v>0.4405632000000001</v>
+      </c>
+      <c r="N16">
+        <v>6.8194368</v>
+      </c>
+      <c r="O16">
+        <v>1.500276096</v>
+      </c>
+      <c r="P16">
+        <v>5.319160704</v>
+      </c>
+      <c r="Q16">
+        <v>7.499160703999999</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1034406452991335</v>
+      </c>
+      <c r="T16">
+        <v>1.405231419546379</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.22</v>
+      </c>
+      <c r="W16">
+        <v>0.034866</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>16.47890699904122</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.0936746683075375</v>
+      </c>
+      <c r="C17">
+        <v>64.38897028259915</v>
+      </c>
+      <c r="D17">
+        <v>67.61897028259915</v>
+      </c>
+      <c r="E17">
+        <v>-4.34</v>
+      </c>
+      <c r="F17">
+        <v>10.56</v>
+      </c>
+      <c r="G17">
+        <v>7.33</v>
+      </c>
+      <c r="H17">
+        <v>55.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>9.44</v>
+      </c>
+      <c r="K17">
+        <v>2.18</v>
+      </c>
+      <c r="L17">
+        <v>7.26</v>
+      </c>
+      <c r="M17">
+        <v>0.4720320000000001</v>
+      </c>
+      <c r="N17">
+        <v>6.787967999999999</v>
+      </c>
+      <c r="O17">
+        <v>1.49335296</v>
+      </c>
+      <c r="P17">
+        <v>5.294615039999999</v>
+      </c>
+      <c r="Q17">
+        <v>7.474615039999999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.104052668597103</v>
+      </c>
+      <c r="T17">
+        <v>1.418536273850064</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.22</v>
+      </c>
+      <c r="W17">
+        <v>0.034866</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>15.38031319910514</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09350914165782025</v>
+      </c>
+      <c r="C18">
+        <v>63.88955659612997</v>
+      </c>
+      <c r="D18">
+        <v>67.82355659612998</v>
+      </c>
+      <c r="E18">
+        <v>-3.635999999999999</v>
+      </c>
+      <c r="F18">
+        <v>11.264</v>
+      </c>
+      <c r="G18">
+        <v>7.33</v>
+      </c>
+      <c r="H18">
+        <v>55.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>9.44</v>
+      </c>
+      <c r="K18">
+        <v>2.18</v>
+      </c>
+      <c r="L18">
+        <v>7.26</v>
+      </c>
+      <c r="M18">
+        <v>0.5035008000000001</v>
+      </c>
+      <c r="N18">
+        <v>6.756499199999999</v>
+      </c>
+      <c r="O18">
+        <v>1.486429824</v>
+      </c>
+      <c r="P18">
+        <v>5.270069375999999</v>
+      </c>
+      <c r="Q18">
+        <v>7.450069375999999</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1046792638783575</v>
+      </c>
+      <c r="T18">
+        <v>1.432157910399075</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.22</v>
+      </c>
+      <c r="W18">
+        <v>0.034866</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>14.41904362416107</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09334361500810301</v>
+      </c>
+      <c r="C19">
+        <v>63.39138464939701</v>
+      </c>
+      <c r="D19">
+        <v>68.02938464939702</v>
+      </c>
+      <c r="E19">
+        <v>-2.931999999999999</v>
+      </c>
+      <c r="F19">
+        <v>11.968</v>
+      </c>
+      <c r="G19">
+        <v>7.33</v>
+      </c>
+      <c r="H19">
+        <v>55.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>9.44</v>
+      </c>
+      <c r="K19">
+        <v>2.18</v>
+      </c>
+      <c r="L19">
+        <v>7.26</v>
+      </c>
+      <c r="M19">
+        <v>0.5349696000000002</v>
+      </c>
+      <c r="N19">
+        <v>6.7250304</v>
+      </c>
+      <c r="O19">
+        <v>1.479506688</v>
+      </c>
+      <c r="P19">
+        <v>5.245523712</v>
+      </c>
+      <c r="Q19">
+        <v>7.425523711999999</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.105320957841088</v>
+      </c>
+      <c r="T19">
+        <v>1.446107779154086</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.22</v>
+      </c>
+      <c r="W19">
+        <v>0.034866</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>13.57086458744571</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09317808835838574</v>
+      </c>
+      <c r="C20">
+        <v>62.89446578195039</v>
+      </c>
+      <c r="D20">
+        <v>68.23646578195039</v>
+      </c>
+      <c r="E20">
+        <v>-2.228</v>
+      </c>
+      <c r="F20">
+        <v>12.672</v>
+      </c>
+      <c r="G20">
+        <v>7.33</v>
+      </c>
+      <c r="H20">
+        <v>55.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>9.44</v>
+      </c>
+      <c r="K20">
+        <v>2.18</v>
+      </c>
+      <c r="L20">
+        <v>7.26</v>
+      </c>
+      <c r="M20">
+        <v>0.5664384000000001</v>
+      </c>
+      <c r="N20">
+        <v>6.6935616</v>
+      </c>
+      <c r="O20">
+        <v>1.472583552</v>
+      </c>
+      <c r="P20">
+        <v>5.220978048</v>
+      </c>
+      <c r="Q20">
+        <v>7.400978048</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1059783028760802</v>
+      </c>
+      <c r="T20">
+        <v>1.460397888610439</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.22</v>
+      </c>
+      <c r="W20">
+        <v>0.034866</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>12.81692766592095</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.09317558170866851</v>
+      </c>
+      <c r="C21">
+        <v>62.19361140195632</v>
+      </c>
+      <c r="D21">
+        <v>68.23961140195632</v>
+      </c>
+      <c r="E21">
+        <v>-1.523999999999999</v>
+      </c>
+      <c r="F21">
+        <v>13.376</v>
+      </c>
+      <c r="G21">
+        <v>7.33</v>
+      </c>
+      <c r="H21">
+        <v>55.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>9.44</v>
+      </c>
+      <c r="K21">
+        <v>2.18</v>
+      </c>
+      <c r="L21">
+        <v>7.26</v>
+      </c>
+      <c r="M21">
+        <v>0.6126208000000001</v>
+      </c>
+      <c r="N21">
+        <v>6.6473792</v>
+      </c>
+      <c r="O21">
+        <v>1.462423424</v>
+      </c>
+      <c r="P21">
+        <v>5.184955776</v>
+      </c>
+      <c r="Q21">
+        <v>7.364955776</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1066518786526772</v>
+      </c>
+      <c r="T21">
+        <v>1.475040840275591</v>
+      </c>
+      <c r="U21">
+        <v>0.0458</v>
+      </c>
+      <c r="V21">
+        <v>0.22</v>
+      </c>
+      <c r="W21">
+        <v>0.035724</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>11.8507239715008</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.09301863505895125</v>
+      </c>
+      <c r="C22">
+        <v>61.68714456331128</v>
+      </c>
+      <c r="D22">
+        <v>68.43714456331128</v>
+      </c>
+      <c r="E22">
+        <v>-0.8199999999999985</v>
+      </c>
+      <c r="F22">
+        <v>14.08</v>
+      </c>
+      <c r="G22">
+        <v>7.33</v>
+      </c>
+      <c r="H22">
+        <v>55.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>9.44</v>
+      </c>
+      <c r="K22">
+        <v>2.18</v>
+      </c>
+      <c r="L22">
+        <v>7.26</v>
+      </c>
+      <c r="M22">
+        <v>0.6448640000000001</v>
+      </c>
+      <c r="N22">
+        <v>6.615136</v>
+      </c>
+      <c r="O22">
+        <v>1.45532992</v>
+      </c>
+      <c r="P22">
+        <v>5.15980608</v>
+      </c>
+      <c r="Q22">
+        <v>7.33980608</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1073422938236891</v>
+      </c>
+      <c r="T22">
+        <v>1.490049865732371</v>
+      </c>
+      <c r="U22">
+        <v>0.0458</v>
+      </c>
+      <c r="V22">
+        <v>0.22</v>
+      </c>
+      <c r="W22">
+        <v>0.035724</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>11.25818777292576</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09286168840923401</v>
+      </c>
+      <c r="C23">
+        <v>61.1818246428922</v>
+      </c>
+      <c r="D23">
+        <v>68.6358246428922</v>
+      </c>
+      <c r="E23">
+        <v>-0.1159999999999997</v>
+      </c>
+      <c r="F23">
+        <v>14.784</v>
+      </c>
+      <c r="G23">
+        <v>7.33</v>
+      </c>
+      <c r="H23">
+        <v>55.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>9.44</v>
+      </c>
+      <c r="K23">
+        <v>2.18</v>
+      </c>
+      <c r="L23">
+        <v>7.26</v>
+      </c>
+      <c r="M23">
+        <v>0.6771072</v>
+      </c>
+      <c r="N23">
+        <v>6.5828928</v>
+      </c>
+      <c r="O23">
+        <v>1.448236416</v>
+      </c>
+      <c r="P23">
+        <v>5.134656383999999</v>
+      </c>
+      <c r="Q23">
+        <v>7.314656383999999</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1080501878597899</v>
+      </c>
+      <c r="T23">
+        <v>1.505438866517171</v>
+      </c>
+      <c r="U23">
+        <v>0.0458</v>
+      </c>
+      <c r="V23">
+        <v>0.22</v>
+      </c>
+      <c r="W23">
+        <v>0.035724</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>10.72208359326263</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.09270474175951675</v>
+      </c>
+      <c r="C24">
+        <v>60.67766165864752</v>
+      </c>
+      <c r="D24">
+        <v>68.83566165864752</v>
+      </c>
+      <c r="E24">
+        <v>0.588000000000001</v>
+      </c>
+      <c r="F24">
+        <v>15.488</v>
+      </c>
+      <c r="G24">
+        <v>7.33</v>
+      </c>
+      <c r="H24">
+        <v>55.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>9.44</v>
+      </c>
+      <c r="K24">
+        <v>2.18</v>
+      </c>
+      <c r="L24">
+        <v>7.26</v>
+      </c>
+      <c r="M24">
+        <v>0.7093504</v>
+      </c>
+      <c r="N24">
+        <v>6.5506496</v>
+      </c>
+      <c r="O24">
+        <v>1.441142912</v>
+      </c>
+      <c r="P24">
+        <v>5.109506688</v>
+      </c>
+      <c r="Q24">
+        <v>7.289506687999999</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1087762330250215</v>
+      </c>
+      <c r="T24">
+        <v>1.521222457065684</v>
+      </c>
+      <c r="U24">
+        <v>0.0458</v>
+      </c>
+      <c r="V24">
+        <v>0.22</v>
+      </c>
+      <c r="W24">
+        <v>0.035724</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>10.23471615720524</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.0929424751097995</v>
+      </c>
+      <c r="C25">
+        <v>59.67141222450448</v>
+      </c>
+      <c r="D25">
+        <v>68.53341222450449</v>
+      </c>
+      <c r="E25">
+        <v>1.292000000000003</v>
+      </c>
+      <c r="F25">
+        <v>16.192</v>
+      </c>
+      <c r="G25">
+        <v>7.33</v>
+      </c>
+      <c r="H25">
+        <v>55.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>9.44</v>
+      </c>
+      <c r="K25">
+        <v>2.18</v>
+      </c>
+      <c r="L25">
+        <v>7.26</v>
+      </c>
+      <c r="M25">
+        <v>0.7772160000000002</v>
+      </c>
+      <c r="N25">
+        <v>6.482784</v>
+      </c>
+      <c r="O25">
+        <v>1.42621248</v>
+      </c>
+      <c r="P25">
+        <v>5.056571519999999</v>
+      </c>
+      <c r="Q25">
+        <v>7.236571519999999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1095211365062331</v>
+      </c>
+      <c r="T25">
+        <v>1.537416011005068</v>
+      </c>
+      <c r="U25">
+        <v>0.048</v>
+      </c>
+      <c r="V25">
+        <v>0.22</v>
+      </c>
+      <c r="W25">
+        <v>0.03744</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>9.341032608695649</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.09280268846008224</v>
+      </c>
+      <c r="C26">
+        <v>59.14481183851883</v>
+      </c>
+      <c r="D26">
+        <v>68.71081183851884</v>
+      </c>
+      <c r="E26">
+        <v>1.996</v>
+      </c>
+      <c r="F26">
+        <v>16.896</v>
+      </c>
+      <c r="G26">
+        <v>7.33</v>
+      </c>
+      <c r="H26">
+        <v>55.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>9.44</v>
+      </c>
+      <c r="K26">
+        <v>2.18</v>
+      </c>
+      <c r="L26">
+        <v>7.26</v>
+      </c>
+      <c r="M26">
+        <v>0.8110080000000001</v>
+      </c>
+      <c r="N26">
+        <v>6.448992</v>
+      </c>
+      <c r="O26">
+        <v>1.41877824</v>
+      </c>
+      <c r="P26">
+        <v>5.03021376</v>
+      </c>
+      <c r="Q26">
+        <v>7.210213759999999</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1102856427106345</v>
+      </c>
+      <c r="T26">
+        <v>1.554035711100751</v>
+      </c>
+      <c r="U26">
+        <v>0.048</v>
+      </c>
+      <c r="V26">
+        <v>0.22</v>
+      </c>
+      <c r="W26">
+        <v>0.03744</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>8.951822916666664</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.09266290181036499</v>
+      </c>
+      <c r="C27">
+        <v>58.61913223833827</v>
+      </c>
+      <c r="D27">
+        <v>68.88913223833828</v>
+      </c>
+      <c r="E27">
+        <v>2.700000000000001</v>
+      </c>
+      <c r="F27">
+        <v>17.6</v>
+      </c>
+      <c r="G27">
+        <v>7.33</v>
+      </c>
+      <c r="H27">
+        <v>55.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>9.44</v>
+      </c>
+      <c r="K27">
+        <v>2.18</v>
+      </c>
+      <c r="L27">
+        <v>7.26</v>
+      </c>
+      <c r="M27">
+        <v>0.8448000000000001</v>
+      </c>
+      <c r="N27">
+        <v>6.4152</v>
+      </c>
+      <c r="O27">
+        <v>1.411344</v>
+      </c>
+      <c r="P27">
+        <v>5.003856</v>
+      </c>
+      <c r="Q27">
+        <v>7.183856</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1110705357471533</v>
+      </c>
+      <c r="T27">
+        <v>1.571098603198985</v>
+      </c>
+      <c r="U27">
+        <v>0.048</v>
+      </c>
+      <c r="V27">
+        <v>0.22</v>
+      </c>
+      <c r="W27">
+        <v>0.03744</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>8.593749999999998</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.09252311516064775</v>
+      </c>
+      <c r="C28">
+        <v>58.09438061157071</v>
+      </c>
+      <c r="D28">
+        <v>69.06838061157072</v>
+      </c>
+      <c r="E28">
+        <v>3.404000000000002</v>
+      </c>
+      <c r="F28">
+        <v>18.304</v>
+      </c>
+      <c r="G28">
+        <v>7.33</v>
+      </c>
+      <c r="H28">
+        <v>55.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>9.44</v>
+      </c>
+      <c r="K28">
+        <v>2.18</v>
+      </c>
+      <c r="L28">
+        <v>7.26</v>
+      </c>
+      <c r="M28">
+        <v>0.8785920000000002</v>
+      </c>
+      <c r="N28">
+        <v>6.381408</v>
+      </c>
+      <c r="O28">
+        <v>1.40390976</v>
+      </c>
+      <c r="P28">
+        <v>4.977498239999999</v>
+      </c>
+      <c r="Q28">
+        <v>7.157498239999999</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1118766421089834</v>
+      </c>
+      <c r="T28">
+        <v>1.588622654543118</v>
+      </c>
+      <c r="U28">
+        <v>0.048</v>
+      </c>
+      <c r="V28">
+        <v>0.22</v>
+      </c>
+      <c r="W28">
+        <v>0.03744</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>8.263221153846153</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.09238332851093049</v>
+      </c>
+      <c r="C29">
+        <v>57.57056422082741</v>
+      </c>
+      <c r="D29">
+        <v>69.24856422082742</v>
+      </c>
+      <c r="E29">
+        <v>4.108000000000002</v>
+      </c>
+      <c r="F29">
+        <v>19.008</v>
+      </c>
+      <c r="G29">
+        <v>7.33</v>
+      </c>
+      <c r="H29">
+        <v>55.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>9.44</v>
+      </c>
+      <c r="K29">
+        <v>2.18</v>
+      </c>
+      <c r="L29">
+        <v>7.26</v>
+      </c>
+      <c r="M29">
+        <v>0.9123840000000002</v>
+      </c>
+      <c r="N29">
+        <v>6.347615999999999</v>
+      </c>
+      <c r="O29">
+        <v>1.39647552</v>
+      </c>
+      <c r="P29">
+        <v>4.951140479999999</v>
+      </c>
+      <c r="Q29">
+        <v>7.131140479999999</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1127048335766171</v>
+      </c>
+      <c r="T29">
+        <v>1.60662681688298</v>
+      </c>
+      <c r="U29">
+        <v>0.048</v>
+      </c>
+      <c r="V29">
+        <v>0.22</v>
+      </c>
+      <c r="W29">
+        <v>0.03744</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>7.957175925925924</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.09257114186121324</v>
+      </c>
+      <c r="C30">
+        <v>56.62469089624466</v>
+      </c>
+      <c r="D30">
+        <v>69.00669089624466</v>
+      </c>
+      <c r="E30">
+        <v>4.812000000000003</v>
+      </c>
+      <c r="F30">
+        <v>19.712</v>
+      </c>
+      <c r="G30">
+        <v>7.33</v>
+      </c>
+      <c r="H30">
+        <v>55.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>9.44</v>
+      </c>
+      <c r="K30">
+        <v>2.18</v>
+      </c>
+      <c r="L30">
+        <v>7.26</v>
+      </c>
+      <c r="M30">
+        <v>0.9757440000000002</v>
+      </c>
+      <c r="N30">
+        <v>6.284255999999999</v>
+      </c>
+      <c r="O30">
+        <v>1.38253632</v>
+      </c>
+      <c r="P30">
+        <v>4.901719679999999</v>
+      </c>
+      <c r="Q30">
+        <v>7.081719679999999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1135560303627962</v>
+      </c>
+      <c r="T30">
+        <v>1.625131094843395</v>
+      </c>
+      <c r="U30">
+        <v>0.0495</v>
+      </c>
+      <c r="V30">
+        <v>0.22</v>
+      </c>
+      <c r="W30">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>7.440476190476189</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.09244305521149597</v>
+      </c>
+      <c r="C31">
+        <v>56.08546219441413</v>
+      </c>
+      <c r="D31">
+        <v>69.17146219441413</v>
+      </c>
+      <c r="E31">
+        <v>5.516</v>
+      </c>
+      <c r="F31">
+        <v>20.416</v>
+      </c>
+      <c r="G31">
+        <v>7.33</v>
+      </c>
+      <c r="H31">
+        <v>55.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>9.44</v>
+      </c>
+      <c r="K31">
+        <v>2.18</v>
+      </c>
+      <c r="L31">
+        <v>7.26</v>
+      </c>
+      <c r="M31">
+        <v>1.010592</v>
+      </c>
+      <c r="N31">
+        <v>6.249408</v>
+      </c>
+      <c r="O31">
+        <v>1.37486976</v>
+      </c>
+      <c r="P31">
+        <v>4.87453824</v>
+      </c>
+      <c r="Q31">
+        <v>7.054538239999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1144312045232338</v>
+      </c>
+      <c r="T31">
+        <v>1.6441566200703</v>
+      </c>
+      <c r="U31">
+        <v>0.0495</v>
+      </c>
+      <c r="V31">
+        <v>0.22</v>
+      </c>
+      <c r="W31">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>7.18390804597701</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.09231496856177872</v>
+      </c>
+      <c r="C32">
+        <v>55.54702224399723</v>
+      </c>
+      <c r="D32">
+        <v>69.33702224399724</v>
+      </c>
+      <c r="E32">
+        <v>6.220000000000001</v>
+      </c>
+      <c r="F32">
+        <v>21.12</v>
+      </c>
+      <c r="G32">
+        <v>7.33</v>
+      </c>
+      <c r="H32">
+        <v>55.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>9.44</v>
+      </c>
+      <c r="K32">
+        <v>2.18</v>
+      </c>
+      <c r="L32">
+        <v>7.26</v>
+      </c>
+      <c r="M32">
+        <v>1.04544</v>
+      </c>
+      <c r="N32">
+        <v>6.21456</v>
+      </c>
+      <c r="O32">
+        <v>1.3672032</v>
+      </c>
+      <c r="P32">
+        <v>4.8473568</v>
+      </c>
+      <c r="Q32">
+        <v>7.0273568</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1153313836596839</v>
+      </c>
+      <c r="T32">
+        <v>1.663725731732259</v>
+      </c>
+      <c r="U32">
+        <v>0.0495</v>
+      </c>
+      <c r="V32">
+        <v>0.22</v>
+      </c>
+      <c r="W32">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>6.944444444444443</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.09218688191206147</v>
+      </c>
+      <c r="C33">
+        <v>55.00937672214849</v>
+      </c>
+      <c r="D33">
+        <v>69.50337672214849</v>
+      </c>
+      <c r="E33">
+        <v>6.924000000000001</v>
+      </c>
+      <c r="F33">
+        <v>21.824</v>
+      </c>
+      <c r="G33">
+        <v>7.33</v>
+      </c>
+      <c r="H33">
+        <v>55.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>9.44</v>
+      </c>
+      <c r="K33">
+        <v>2.18</v>
+      </c>
+      <c r="L33">
+        <v>7.26</v>
+      </c>
+      <c r="M33">
+        <v>1.080288</v>
+      </c>
+      <c r="N33">
+        <v>6.179711999999999</v>
+      </c>
+      <c r="O33">
+        <v>1.35953664</v>
+      </c>
+      <c r="P33">
+        <v>4.820175359999999</v>
+      </c>
+      <c r="Q33">
+        <v>7.000175359999999</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1162576549450166</v>
+      </c>
+      <c r="T33">
+        <v>1.683862064022101</v>
+      </c>
+      <c r="U33">
+        <v>0.0495</v>
+      </c>
+      <c r="V33">
+        <v>0.22</v>
+      </c>
+      <c r="W33">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>6.72043010752688</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.09205879526234421</v>
+      </c>
+      <c r="C34">
+        <v>54.47253136063634</v>
+      </c>
+      <c r="D34">
+        <v>69.67053136063635</v>
+      </c>
+      <c r="E34">
+        <v>7.628000000000002</v>
+      </c>
+      <c r="F34">
+        <v>22.528</v>
+      </c>
+      <c r="G34">
+        <v>7.33</v>
+      </c>
+      <c r="H34">
+        <v>55.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>9.44</v>
+      </c>
+      <c r="K34">
+        <v>2.18</v>
+      </c>
+      <c r="L34">
+        <v>7.26</v>
+      </c>
+      <c r="M34">
+        <v>1.115136</v>
+      </c>
+      <c r="N34">
+        <v>6.144864</v>
+      </c>
+      <c r="O34">
+        <v>1.35187008</v>
+      </c>
+      <c r="P34">
+        <v>4.79299392</v>
+      </c>
+      <c r="Q34">
+        <v>6.97299392</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1172111695034474</v>
+      </c>
+      <c r="T34">
+        <v>1.704590641379291</v>
+      </c>
+      <c r="U34">
+        <v>0.0495</v>
+      </c>
+      <c r="V34">
+        <v>0.22</v>
+      </c>
+      <c r="W34">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>6.510416666666666</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.09193070861262696</v>
+      </c>
+      <c r="C35">
+        <v>53.93649194650146</v>
+      </c>
+      <c r="D35">
+        <v>69.83849194650146</v>
+      </c>
+      <c r="E35">
+        <v>8.332000000000003</v>
+      </c>
+      <c r="F35">
+        <v>23.232</v>
+      </c>
+      <c r="G35">
+        <v>7.33</v>
+      </c>
+      <c r="H35">
+        <v>55.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>9.44</v>
+      </c>
+      <c r="K35">
+        <v>2.18</v>
+      </c>
+      <c r="L35">
+        <v>7.26</v>
+      </c>
+      <c r="M35">
+        <v>1.149984</v>
+      </c>
+      <c r="N35">
+        <v>6.110016</v>
+      </c>
+      <c r="O35">
+        <v>1.34420352</v>
+      </c>
+      <c r="P35">
+        <v>4.76581248</v>
+      </c>
+      <c r="Q35">
+        <v>6.94581248</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1181931471830253</v>
+      </c>
+      <c r="T35">
+        <v>1.725937982239681</v>
+      </c>
+      <c r="U35">
+        <v>0.0495</v>
+      </c>
+      <c r="V35">
+        <v>0.22</v>
+      </c>
+      <c r="W35">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>6.313131313131312</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.09217390196290971</v>
+      </c>
+      <c r="C36">
+        <v>52.91427918313693</v>
+      </c>
+      <c r="D36">
+        <v>69.52027918313694</v>
+      </c>
+      <c r="E36">
+        <v>9.036000000000003</v>
+      </c>
+      <c r="F36">
+        <v>23.936</v>
+      </c>
+      <c r="G36">
+        <v>7.33</v>
+      </c>
+      <c r="H36">
+        <v>55.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>9.44</v>
+      </c>
+      <c r="K36">
+        <v>2.18</v>
+      </c>
+      <c r="L36">
+        <v>7.26</v>
+      </c>
+      <c r="M36">
+        <v>1.2183424</v>
+      </c>
+      <c r="N36">
+        <v>6.0416576</v>
+      </c>
+      <c r="O36">
+        <v>1.329164672</v>
+      </c>
+      <c r="P36">
+        <v>4.712492928</v>
+      </c>
+      <c r="Q36">
+        <v>6.892492927999999</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1192048817619844</v>
+      </c>
+      <c r="T36">
+        <v>1.747932212217053</v>
+      </c>
+      <c r="U36">
+        <v>0.0509</v>
+      </c>
+      <c r="V36">
+        <v>0.22</v>
+      </c>
+      <c r="W36">
+        <v>0.039702</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>5.958915982896104</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.09205673531319246</v>
+      </c>
+      <c r="C37">
+        <v>52.3632261888329</v>
+      </c>
+      <c r="D37">
+        <v>69.6732261888329</v>
+      </c>
+      <c r="E37">
+        <v>9.740000000000004</v>
+      </c>
+      <c r="F37">
+        <v>24.64</v>
+      </c>
+      <c r="G37">
+        <v>7.33</v>
+      </c>
+      <c r="H37">
+        <v>55.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>9.44</v>
+      </c>
+      <c r="K37">
+        <v>2.18</v>
+      </c>
+      <c r="L37">
+        <v>7.26</v>
+      </c>
+      <c r="M37">
+        <v>1.254176</v>
+      </c>
+      <c r="N37">
+        <v>6.005824</v>
+      </c>
+      <c r="O37">
+        <v>1.32128128</v>
+      </c>
+      <c r="P37">
+        <v>4.68454272</v>
+      </c>
+      <c r="Q37">
+        <v>6.864542719999999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1202477466356807</v>
+      </c>
+      <c r="T37">
+        <v>1.77060318773219</v>
+      </c>
+      <c r="U37">
+        <v>0.0509</v>
+      </c>
+      <c r="V37">
+        <v>0.22</v>
+      </c>
+      <c r="W37">
+        <v>0.039702</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>5.788661240527644</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.09193956866347522</v>
+      </c>
+      <c r="C38">
+        <v>51.81284765571449</v>
+      </c>
+      <c r="D38">
+        <v>69.82684765571449</v>
+      </c>
+      <c r="E38">
+        <v>10.444</v>
+      </c>
+      <c r="F38">
+        <v>25.344</v>
+      </c>
+      <c r="G38">
+        <v>7.33</v>
+      </c>
+      <c r="H38">
+        <v>55.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>9.44</v>
+      </c>
+      <c r="K38">
+        <v>2.18</v>
+      </c>
+      <c r="L38">
+        <v>7.26</v>
+      </c>
+      <c r="M38">
+        <v>1.2900096</v>
+      </c>
+      <c r="N38">
+        <v>5.969990399999999</v>
+      </c>
+      <c r="O38">
+        <v>1.313397888</v>
+      </c>
+      <c r="P38">
+        <v>4.656592512</v>
+      </c>
+      <c r="Q38">
+        <v>6.836592511999999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.12132320103668</v>
+      </c>
+      <c r="T38">
+        <v>1.793982631232174</v>
+      </c>
+      <c r="U38">
+        <v>0.0509</v>
+      </c>
+      <c r="V38">
+        <v>0.22</v>
+      </c>
+      <c r="W38">
+        <v>0.039702</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>5.627865094957432</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.09182240201375796</v>
+      </c>
+      <c r="C39">
+        <v>51.26314805496864</v>
+      </c>
+      <c r="D39">
+        <v>69.98114805496864</v>
+      </c>
+      <c r="E39">
+        <v>11.148</v>
+      </c>
+      <c r="F39">
+        <v>26.048</v>
+      </c>
+      <c r="G39">
+        <v>7.33</v>
+      </c>
+      <c r="H39">
+        <v>55.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>9.44</v>
+      </c>
+      <c r="K39">
+        <v>2.18</v>
+      </c>
+      <c r="L39">
+        <v>7.26</v>
+      </c>
+      <c r="M39">
+        <v>1.3258432</v>
+      </c>
+      <c r="N39">
+        <v>5.934156799999999</v>
+      </c>
+      <c r="O39">
+        <v>1.305514496</v>
+      </c>
+      <c r="P39">
+        <v>4.628642304</v>
+      </c>
+      <c r="Q39">
+        <v>6.808642303999999</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1224327968472349</v>
+      </c>
+      <c r="T39">
+        <v>1.818104279287715</v>
+      </c>
+      <c r="U39">
+        <v>0.0509</v>
+      </c>
+      <c r="V39">
+        <v>0.22</v>
+      </c>
+      <c r="W39">
+        <v>0.039702</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>5.475760632931555</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.09170523536404071</v>
+      </c>
+      <c r="C40">
+        <v>50.71413189739079</v>
+      </c>
+      <c r="D40">
+        <v>70.1361318973908</v>
+      </c>
+      <c r="E40">
+        <v>11.852</v>
+      </c>
+      <c r="F40">
+        <v>26.752</v>
+      </c>
+      <c r="G40">
+        <v>7.33</v>
+      </c>
+      <c r="H40">
+        <v>55.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>9.44</v>
+      </c>
+      <c r="K40">
+        <v>2.18</v>
+      </c>
+      <c r="L40">
+        <v>7.26</v>
+      </c>
+      <c r="M40">
+        <v>1.3616768</v>
+      </c>
+      <c r="N40">
+        <v>5.8983232</v>
+      </c>
+      <c r="O40">
+        <v>1.297631104</v>
+      </c>
+      <c r="P40">
+        <v>4.600692096</v>
+      </c>
+      <c r="Q40">
+        <v>6.780692096</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1235781860710334</v>
+      </c>
+      <c r="T40">
+        <v>1.843004045022465</v>
+      </c>
+      <c r="U40">
+        <v>0.0509</v>
+      </c>
+      <c r="V40">
+        <v>0.22</v>
+      </c>
+      <c r="W40">
+        <v>0.039702</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>5.331661668907041</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.09158806871432347</v>
+      </c>
+      <c r="C41">
+        <v>50.16580373382443</v>
+      </c>
+      <c r="D41">
+        <v>70.29180373382444</v>
+      </c>
+      <c r="E41">
+        <v>12.556</v>
+      </c>
+      <c r="F41">
+        <v>27.456</v>
+      </c>
+      <c r="G41">
+        <v>7.33</v>
+      </c>
+      <c r="H41">
+        <v>55.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>9.44</v>
+      </c>
+      <c r="K41">
+        <v>2.18</v>
+      </c>
+      <c r="L41">
+        <v>7.26</v>
+      </c>
+      <c r="M41">
+        <v>1.3975104</v>
+      </c>
+      <c r="N41">
+        <v>5.8624896</v>
+      </c>
+      <c r="O41">
+        <v>1.289747712</v>
+      </c>
+      <c r="P41">
+        <v>4.572741887999999</v>
+      </c>
+      <c r="Q41">
+        <v>6.752741887999999</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1247611290398745</v>
+      </c>
+      <c r="T41">
+        <v>1.868720196519012</v>
+      </c>
+      <c r="U41">
+        <v>0.0509</v>
+      </c>
+      <c r="V41">
+        <v>0.22</v>
+      </c>
+      <c r="W41">
+        <v>0.039702</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>5.194952395345322</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.0914709020646062</v>
+      </c>
+      <c r="C42">
+        <v>49.61816815560658</v>
+      </c>
+      <c r="D42">
+        <v>70.44816815560658</v>
+      </c>
+      <c r="E42">
+        <v>13.26</v>
+      </c>
+      <c r="F42">
+        <v>28.16</v>
+      </c>
+      <c r="G42">
+        <v>7.33</v>
+      </c>
+      <c r="H42">
+        <v>55.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>9.44</v>
+      </c>
+      <c r="K42">
+        <v>2.18</v>
+      </c>
+      <c r="L42">
+        <v>7.26</v>
+      </c>
+      <c r="M42">
+        <v>1.433344</v>
+      </c>
+      <c r="N42">
+        <v>5.826656</v>
+      </c>
+      <c r="O42">
+        <v>1.28186432</v>
+      </c>
+      <c r="P42">
+        <v>4.544791679999999</v>
+      </c>
+      <c r="Q42">
+        <v>6.724791679999999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1259835034410103</v>
+      </c>
+      <c r="T42">
+        <v>1.895293553065442</v>
+      </c>
+      <c r="U42">
+        <v>0.0509</v>
+      </c>
+      <c r="V42">
+        <v>0.22</v>
+      </c>
+      <c r="W42">
+        <v>0.039702</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>5.065078585461689</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.09135373541488896</v>
+      </c>
+      <c r="C43">
+        <v>49.07122979501899</v>
+      </c>
+      <c r="D43">
+        <v>70.605229795019</v>
+      </c>
+      <c r="E43">
+        <v>13.964</v>
+      </c>
+      <c r="F43">
+        <v>28.864</v>
+      </c>
+      <c r="G43">
+        <v>7.33</v>
+      </c>
+      <c r="H43">
+        <v>55.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>9.44</v>
+      </c>
+      <c r="K43">
+        <v>2.18</v>
+      </c>
+      <c r="L43">
+        <v>7.26</v>
+      </c>
+      <c r="M43">
+        <v>1.4691776</v>
+      </c>
+      <c r="N43">
+        <v>5.7908224</v>
+      </c>
+      <c r="O43">
+        <v>1.273980928</v>
+      </c>
+      <c r="P43">
+        <v>4.516841471999999</v>
+      </c>
+      <c r="Q43">
+        <v>6.696841471999999</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1272473142625237</v>
+      </c>
+      <c r="T43">
+        <v>1.92276770135921</v>
+      </c>
+      <c r="U43">
+        <v>0.0509</v>
+      </c>
+      <c r="V43">
+        <v>0.22</v>
+      </c>
+      <c r="W43">
+        <v>0.039702</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>4.941540083377257</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.09123656876517172</v>
+      </c>
+      <c r="C44">
+        <v>48.52499332574591</v>
+      </c>
+      <c r="D44">
+        <v>70.76299332574591</v>
+      </c>
+      <c r="E44">
+        <v>14.668</v>
+      </c>
+      <c r="F44">
+        <v>29.568</v>
+      </c>
+      <c r="G44">
+        <v>7.33</v>
+      </c>
+      <c r="H44">
+        <v>55.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>9.44</v>
+      </c>
+      <c r="K44">
+        <v>2.18</v>
+      </c>
+      <c r="L44">
+        <v>7.26</v>
+      </c>
+      <c r="M44">
+        <v>1.5050112</v>
+      </c>
+      <c r="N44">
+        <v>5.7549888</v>
+      </c>
+      <c r="O44">
+        <v>1.266097536</v>
+      </c>
+      <c r="P44">
+        <v>4.488891263999999</v>
+      </c>
+      <c r="Q44">
+        <v>6.668891263999999</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1285547047675374</v>
+      </c>
+      <c r="T44">
+        <v>1.951189234076901</v>
+      </c>
+      <c r="U44">
+        <v>0.0509</v>
+      </c>
+      <c r="V44">
+        <v>0.22</v>
+      </c>
+      <c r="W44">
+        <v>0.039702</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>4.823884367106371</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.09111940211545447</v>
+      </c>
+      <c r="C45">
+        <v>47.97946346333742</v>
+      </c>
+      <c r="D45">
+        <v>70.92146346333743</v>
+      </c>
+      <c r="E45">
+        <v>15.372</v>
+      </c>
+      <c r="F45">
+        <v>30.272</v>
+      </c>
+      <c r="G45">
+        <v>7.33</v>
+      </c>
+      <c r="H45">
+        <v>55.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>9.44</v>
+      </c>
+      <c r="K45">
+        <v>2.18</v>
+      </c>
+      <c r="L45">
+        <v>7.26</v>
+      </c>
+      <c r="M45">
+        <v>1.5408448</v>
+      </c>
+      <c r="N45">
+        <v>5.719155199999999</v>
+      </c>
+      <c r="O45">
+        <v>1.258214144</v>
+      </c>
+      <c r="P45">
+        <v>4.460941055999999</v>
+      </c>
+      <c r="Q45">
+        <v>6.640941055999999</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1299079686236043</v>
+      </c>
+      <c r="T45">
+        <v>1.980608013556616</v>
+      </c>
+      <c r="U45">
+        <v>0.0509</v>
+      </c>
+      <c r="V45">
+        <v>0.22</v>
+      </c>
+      <c r="W45">
+        <v>0.039702</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>4.711701009731804</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.09100223546573721</v>
+      </c>
+      <c r="C46">
+        <v>47.43464496567938</v>
+      </c>
+      <c r="D46">
+        <v>71.08064496567938</v>
+      </c>
+      <c r="E46">
+        <v>16.076</v>
+      </c>
+      <c r="F46">
+        <v>30.976</v>
+      </c>
+      <c r="G46">
+        <v>7.33</v>
+      </c>
+      <c r="H46">
+        <v>55.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>9.44</v>
+      </c>
+      <c r="K46">
+        <v>2.18</v>
+      </c>
+      <c r="L46">
+        <v>7.26</v>
+      </c>
+      <c r="M46">
+        <v>1.5766784</v>
+      </c>
+      <c r="N46">
+        <v>5.683321599999999</v>
+      </c>
+      <c r="O46">
+        <v>1.250330752</v>
+      </c>
+      <c r="P46">
+        <v>4.432990847999999</v>
+      </c>
+      <c r="Q46">
+        <v>6.612990847999999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1313095633316736</v>
+      </c>
+      <c r="T46">
+        <v>2.011077463732034</v>
+      </c>
+      <c r="U46">
+        <v>0.0509</v>
+      </c>
+      <c r="V46">
+        <v>0.22</v>
+      </c>
+      <c r="W46">
+        <v>0.039702</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>4.604616895874262</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.09088506881601996</v>
+      </c>
+      <c r="C47">
+        <v>46.89054263346951</v>
+      </c>
+      <c r="D47">
+        <v>71.24054263346952</v>
+      </c>
+      <c r="E47">
+        <v>16.78</v>
+      </c>
+      <c r="F47">
+        <v>31.68</v>
+      </c>
+      <c r="G47">
+        <v>7.33</v>
+      </c>
+      <c r="H47">
+        <v>55.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>9.44</v>
+      </c>
+      <c r="K47">
+        <v>2.18</v>
+      </c>
+      <c r="L47">
+        <v>7.26</v>
+      </c>
+      <c r="M47">
+        <v>1.612512</v>
+      </c>
+      <c r="N47">
+        <v>5.647487999999999</v>
+      </c>
+      <c r="O47">
+        <v>1.24244736</v>
+      </c>
+      <c r="P47">
+        <v>4.405040639999999</v>
+      </c>
+      <c r="Q47">
+        <v>6.585040639999999</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1327621251200363</v>
+      </c>
+      <c r="T47">
+        <v>2.042654893913832</v>
+      </c>
+      <c r="U47">
+        <v>0.0509</v>
+      </c>
+      <c r="V47">
+        <v>0.22</v>
+      </c>
+      <c r="W47">
+        <v>0.039702</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>4.502292075965945</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.0917007821663027</v>
+      </c>
+      <c r="C48">
+        <v>45.08803597009308</v>
+      </c>
+      <c r="D48">
+        <v>70.14203597009309</v>
+      </c>
+      <c r="E48">
+        <v>17.48400000000001</v>
+      </c>
+      <c r="F48">
+        <v>32.38400000000001</v>
+      </c>
+      <c r="G48">
+        <v>7.33</v>
+      </c>
+      <c r="H48">
+        <v>55.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>9.44</v>
+      </c>
+      <c r="K48">
+        <v>2.18</v>
+      </c>
+      <c r="L48">
+        <v>7.26</v>
+      </c>
+      <c r="M48">
+        <v>1.732544</v>
+      </c>
+      <c r="N48">
+        <v>5.527455999999999</v>
+      </c>
+      <c r="O48">
+        <v>1.21604032</v>
+      </c>
+      <c r="P48">
+        <v>4.31141568</v>
+      </c>
+      <c r="Q48">
+        <v>6.491415679999999</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1342684854931532</v>
+      </c>
+      <c r="T48">
+        <v>2.075401858546808</v>
+      </c>
+      <c r="U48">
+        <v>0.0535</v>
+      </c>
+      <c r="V48">
+        <v>0.22</v>
+      </c>
+      <c r="W48">
+        <v>0.04173</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>4.190369768386834</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.09160389551658546</v>
+      </c>
+      <c r="C49">
+        <v>44.51273531704474</v>
+      </c>
+      <c r="D49">
+        <v>70.27073531704475</v>
+      </c>
+      <c r="E49">
+        <v>18.18800000000001</v>
+      </c>
+      <c r="F49">
+        <v>33.08800000000001</v>
+      </c>
+      <c r="G49">
+        <v>7.33</v>
+      </c>
+      <c r="H49">
+        <v>55.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>9.44</v>
+      </c>
+      <c r="K49">
+        <v>2.18</v>
+      </c>
+      <c r="L49">
+        <v>7.26</v>
+      </c>
+      <c r="M49">
+        <v>1.770208</v>
+      </c>
+      <c r="N49">
+        <v>5.489792</v>
+      </c>
+      <c r="O49">
+        <v>1.20775424</v>
+      </c>
+      <c r="P49">
+        <v>4.28203776</v>
+      </c>
+      <c r="Q49">
+        <v>6.462037759999999</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1358316896539348</v>
+      </c>
+      <c r="T49">
+        <v>2.109384557694235</v>
+      </c>
+      <c r="U49">
+        <v>0.0535</v>
+      </c>
+      <c r="V49">
+        <v>0.22</v>
+      </c>
+      <c r="W49">
+        <v>0.04173</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>4.101212964804136</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.0915070088668682</v>
+      </c>
+      <c r="C50">
+        <v>43.93790781733279</v>
+      </c>
+      <c r="D50">
+        <v>70.39990781733279</v>
+      </c>
+      <c r="E50">
+        <v>18.892</v>
+      </c>
+      <c r="F50">
+        <v>33.792</v>
+      </c>
+      <c r="G50">
+        <v>7.33</v>
+      </c>
+      <c r="H50">
+        <v>55.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>9.44</v>
+      </c>
+      <c r="K50">
+        <v>2.18</v>
+      </c>
+      <c r="L50">
+        <v>7.26</v>
+      </c>
+      <c r="M50">
+        <v>1.807872</v>
+      </c>
+      <c r="N50">
+        <v>5.452128</v>
+      </c>
+      <c r="O50">
+        <v>1.19946816</v>
+      </c>
+      <c r="P50">
+        <v>4.25265984</v>
+      </c>
+      <c r="Q50">
+        <v>6.432659839999999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1374550170516696</v>
+      </c>
+      <c r="T50">
+        <v>2.144674283731948</v>
+      </c>
+      <c r="U50">
+        <v>0.0535</v>
+      </c>
+      <c r="V50">
+        <v>0.22</v>
+      </c>
+      <c r="W50">
+        <v>0.04173</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>4.015771028037383</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.09244206221715096</v>
+      </c>
+      <c r="C51">
+        <v>42.00674266104715</v>
+      </c>
+      <c r="D51">
+        <v>69.17274266104715</v>
+      </c>
+      <c r="E51">
+        <v>19.596</v>
+      </c>
+      <c r="F51">
+        <v>34.496</v>
+      </c>
+      <c r="G51">
+        <v>7.33</v>
+      </c>
+      <c r="H51">
+        <v>55.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>9.44</v>
+      </c>
+      <c r="K51">
+        <v>2.18</v>
+      </c>
+      <c r="L51">
+        <v>7.26</v>
+      </c>
+      <c r="M51">
+        <v>1.9386752</v>
+      </c>
+      <c r="N51">
+        <v>5.321324799999999</v>
+      </c>
+      <c r="O51">
+        <v>1.170691456</v>
+      </c>
+      <c r="P51">
+        <v>4.150633343999999</v>
+      </c>
+      <c r="Q51">
+        <v>6.330633343999999</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1391420043473548</v>
+      </c>
+      <c r="T51">
+        <v>2.18134792059467</v>
+      </c>
+      <c r="U51">
+        <v>0.0562</v>
+      </c>
+      <c r="V51">
+        <v>0.22</v>
+      </c>
+      <c r="W51">
+        <v>0.043836</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>3.744825332268138</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.0923662355674337</v>
+      </c>
+      <c r="C52">
+        <v>41.40066138302151</v>
+      </c>
+      <c r="D52">
+        <v>69.27066138302152</v>
+      </c>
+      <c r="E52">
+        <v>20.3</v>
+      </c>
+      <c r="F52">
+        <v>35.2</v>
+      </c>
+      <c r="G52">
+        <v>7.33</v>
+      </c>
+      <c r="H52">
+        <v>55.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>9.44</v>
+      </c>
+      <c r="K52">
+        <v>2.18</v>
+      </c>
+      <c r="L52">
+        <v>7.26</v>
+      </c>
+      <c r="M52">
+        <v>1.97824</v>
+      </c>
+      <c r="N52">
+        <v>5.281759999999999</v>
+      </c>
+      <c r="O52">
+        <v>1.1619872</v>
+      </c>
+      <c r="P52">
+        <v>4.1197728</v>
+      </c>
+      <c r="Q52">
+        <v>6.2997728</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1408964711348674</v>
+      </c>
+      <c r="T52">
+        <v>2.2194885029319</v>
+      </c>
+      <c r="U52">
+        <v>0.0562</v>
+      </c>
+      <c r="V52">
+        <v>0.22</v>
+      </c>
+      <c r="W52">
+        <v>0.043836</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>3.669928825622775</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.09229040891771645</v>
+      </c>
+      <c r="C53">
+        <v>40.79485771919934</v>
+      </c>
+      <c r="D53">
+        <v>69.36885771919934</v>
+      </c>
+      <c r="E53">
+        <v>21.004</v>
+      </c>
+      <c r="F53">
+        <v>35.904</v>
+      </c>
+      <c r="G53">
+        <v>7.33</v>
+      </c>
+      <c r="H53">
+        <v>55.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>9.44</v>
+      </c>
+      <c r="K53">
+        <v>2.18</v>
+      </c>
+      <c r="L53">
+        <v>7.26</v>
+      </c>
+      <c r="M53">
+        <v>2.0178048</v>
+      </c>
+      <c r="N53">
+        <v>5.242195199999999</v>
+      </c>
+      <c r="O53">
+        <v>1.153282944</v>
+      </c>
+      <c r="P53">
+        <v>4.088912256</v>
+      </c>
+      <c r="Q53">
+        <v>6.268912255999999</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1427225488116662</v>
+      </c>
+      <c r="T53">
+        <v>2.259185843731874</v>
+      </c>
+      <c r="U53">
+        <v>0.0562</v>
+      </c>
+      <c r="V53">
+        <v>0.22</v>
+      </c>
+      <c r="W53">
+        <v>0.043836</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>3.597969436885073</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.0922145822679992</v>
+      </c>
+      <c r="C54">
+        <v>40.18933285187319</v>
+      </c>
+      <c r="D54">
+        <v>69.46733285187319</v>
+      </c>
+      <c r="E54">
+        <v>21.70800000000001</v>
+      </c>
+      <c r="F54">
+        <v>36.608</v>
+      </c>
+      <c r="G54">
+        <v>7.33</v>
+      </c>
+      <c r="H54">
+        <v>55.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>9.44</v>
+      </c>
+      <c r="K54">
+        <v>2.18</v>
+      </c>
+      <c r="L54">
+        <v>7.26</v>
+      </c>
+      <c r="M54">
+        <v>2.0573696</v>
+      </c>
+      <c r="N54">
+        <v>5.202630399999999</v>
+      </c>
+      <c r="O54">
+        <v>1.144578688</v>
+      </c>
+      <c r="P54">
+        <v>4.058051711999999</v>
+      </c>
+      <c r="Q54">
+        <v>6.238051711999999</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1446247130583317</v>
+      </c>
+      <c r="T54">
+        <v>2.300537240398514</v>
+      </c>
+      <c r="U54">
+        <v>0.0562</v>
+      </c>
+      <c r="V54">
+        <v>0.22</v>
+      </c>
+      <c r="W54">
+        <v>0.043836</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>3.528777716944976</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.09408173561828194</v>
+      </c>
+      <c r="C55">
+        <v>37.13905768849558</v>
+      </c>
+      <c r="D55">
+        <v>67.12105768849558</v>
+      </c>
+      <c r="E55">
+        <v>22.41200000000001</v>
+      </c>
+      <c r="F55">
+        <v>37.312</v>
+      </c>
+      <c r="G55">
+        <v>7.33</v>
+      </c>
+      <c r="H55">
+        <v>55.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>9.44</v>
+      </c>
+      <c r="K55">
+        <v>2.18</v>
+      </c>
+      <c r="L55">
+        <v>7.26</v>
+      </c>
+      <c r="M55">
+        <v>2.2723008</v>
+      </c>
+      <c r="N55">
+        <v>4.9876992</v>
+      </c>
+      <c r="O55">
+        <v>1.097293824</v>
+      </c>
+      <c r="P55">
+        <v>3.890405376</v>
+      </c>
+      <c r="Q55">
+        <v>6.070405376</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1466078204644297</v>
+      </c>
+      <c r="T55">
+        <v>2.343648270965862</v>
+      </c>
+      <c r="U55">
+        <v>0.0609</v>
+      </c>
+      <c r="V55">
+        <v>0.22</v>
+      </c>
+      <c r="W55">
+        <v>0.047502</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>3.194999535272794</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.09404256896856469</v>
+      </c>
+      <c r="C56">
+        <v>36.48264611539572</v>
+      </c>
+      <c r="D56">
+        <v>67.16864611539573</v>
+      </c>
+      <c r="E56">
+        <v>23.11600000000001</v>
+      </c>
+      <c r="F56">
+        <v>38.01600000000001</v>
+      </c>
+      <c r="G56">
+        <v>7.33</v>
+      </c>
+      <c r="H56">
+        <v>55.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>9.44</v>
+      </c>
+      <c r="K56">
+        <v>2.18</v>
+      </c>
+      <c r="L56">
+        <v>7.26</v>
+      </c>
+      <c r="M56">
+        <v>2.315174400000001</v>
+      </c>
+      <c r="N56">
+        <v>4.9448256</v>
+      </c>
+      <c r="O56">
+        <v>1.087861632</v>
+      </c>
+      <c r="P56">
+        <v>3.856963968</v>
+      </c>
+      <c r="Q56">
+        <v>6.036963967999999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1486771499316624</v>
+      </c>
+      <c r="T56">
+        <v>2.388633694166573</v>
+      </c>
+      <c r="U56">
+        <v>0.0609</v>
+      </c>
+      <c r="V56">
+        <v>0.22</v>
+      </c>
+      <c r="W56">
+        <v>0.047502</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>3.135832877212187</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.09400340231884743</v>
+      </c>
+      <c r="C57">
+        <v>35.8263020699905</v>
+      </c>
+      <c r="D57">
+        <v>67.2163020699905</v>
+      </c>
+      <c r="E57">
+        <v>23.82000000000001</v>
+      </c>
+      <c r="F57">
+        <v>38.72000000000001</v>
+      </c>
+      <c r="G57">
+        <v>7.33</v>
+      </c>
+      <c r="H57">
+        <v>55.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>9.44</v>
+      </c>
+      <c r="K57">
+        <v>2.18</v>
+      </c>
+      <c r="L57">
+        <v>7.26</v>
+      </c>
+      <c r="M57">
+        <v>2.358048000000001</v>
+      </c>
+      <c r="N57">
+        <v>4.901952</v>
+      </c>
+      <c r="O57">
+        <v>1.07842944</v>
+      </c>
+      <c r="P57">
+        <v>3.82352256</v>
+      </c>
+      <c r="Q57">
+        <v>6.00352256</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1508384495974388</v>
+      </c>
+      <c r="T57">
+        <v>2.435618469509538</v>
+      </c>
+      <c r="U57">
+        <v>0.0609</v>
+      </c>
+      <c r="V57">
+        <v>0.22</v>
+      </c>
+      <c r="W57">
+        <v>0.047502</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>3.078817733990147</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.09396423566913019</v>
+      </c>
+      <c r="C58">
+        <v>35.17002569611402</v>
+      </c>
+      <c r="D58">
+        <v>67.26402569611403</v>
+      </c>
+      <c r="E58">
+        <v>24.52400000000001</v>
+      </c>
+      <c r="F58">
+        <v>39.42400000000001</v>
+      </c>
+      <c r="G58">
+        <v>7.33</v>
+      </c>
+      <c r="H58">
+        <v>55.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>9.44</v>
+      </c>
+      <c r="K58">
+        <v>2.18</v>
+      </c>
+      <c r="L58">
+        <v>7.26</v>
+      </c>
+      <c r="M58">
+        <v>2.400921600000001</v>
+      </c>
+      <c r="N58">
+        <v>4.8590784</v>
+      </c>
+      <c r="O58">
+        <v>1.068997248</v>
+      </c>
+      <c r="P58">
+        <v>3.790081152</v>
+      </c>
+      <c r="Q58">
+        <v>5.970081152</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1530979901571141</v>
+      </c>
+      <c r="T58">
+        <v>2.484738916459001</v>
+      </c>
+      <c r="U58">
+        <v>0.0609</v>
+      </c>
+      <c r="V58">
+        <v>0.22</v>
+      </c>
+      <c r="W58">
+        <v>0.047502</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>3.02383884588318</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.09805984901941293</v>
+      </c>
+      <c r="C59">
+        <v>29.81722138436968</v>
+      </c>
+      <c r="D59">
+        <v>62.61522138436968</v>
+      </c>
+      <c r="E59">
+        <v>25.22800000000001</v>
+      </c>
+      <c r="F59">
+        <v>40.12800000000001</v>
+      </c>
+      <c r="G59">
+        <v>7.33</v>
+      </c>
+      <c r="H59">
+        <v>55.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>9.44</v>
+      </c>
+      <c r="K59">
+        <v>2.18</v>
+      </c>
+      <c r="L59">
+        <v>7.26</v>
+      </c>
+      <c r="M59">
+        <v>2.816985600000001</v>
+      </c>
+      <c r="N59">
+        <v>4.443014399999999</v>
+      </c>
+      <c r="O59">
+        <v>0.9774631679999998</v>
+      </c>
+      <c r="P59">
+        <v>3.465551231999999</v>
+      </c>
+      <c r="Q59">
+        <v>5.645551231999999</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1554626256265417</v>
+      </c>
+      <c r="T59">
+        <v>2.536144035359603</v>
+      </c>
+      <c r="U59">
+        <v>0.0702</v>
+      </c>
+      <c r="V59">
+        <v>0.22</v>
+      </c>
+      <c r="W59">
+        <v>0.054756</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>2.577222971959813</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.0980932223696957</v>
+      </c>
+      <c r="C60">
+        <v>29.07797823797322</v>
+      </c>
+      <c r="D60">
+        <v>62.57997823797322</v>
+      </c>
+      <c r="E60">
+        <v>25.932</v>
+      </c>
+      <c r="F60">
+        <v>40.832</v>
+      </c>
+      <c r="G60">
+        <v>7.33</v>
+      </c>
+      <c r="H60">
+        <v>55.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>9.44</v>
+      </c>
+      <c r="K60">
+        <v>2.18</v>
+      </c>
+      <c r="L60">
+        <v>7.26</v>
+      </c>
+      <c r="M60">
+        <v>2.8664064</v>
+      </c>
+      <c r="N60">
+        <v>4.3935936</v>
+      </c>
+      <c r="O60">
+        <v>0.966590592</v>
+      </c>
+      <c r="P60">
+        <v>3.427003008</v>
+      </c>
+      <c r="Q60">
+        <v>5.607003008</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1579398627849897</v>
+      </c>
+      <c r="T60">
+        <v>2.589997017064994</v>
+      </c>
+      <c r="U60">
+        <v>0.0702</v>
+      </c>
+      <c r="V60">
+        <v>0.22</v>
+      </c>
+      <c r="W60">
+        <v>0.054756</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>2.532788093132921</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1002895357199784</v>
+      </c>
+      <c r="C61">
+        <v>26.13871592780741</v>
+      </c>
+      <c r="D61">
+        <v>60.34471592780741</v>
+      </c>
+      <c r="E61">
+        <v>26.636</v>
+      </c>
+      <c r="F61">
+        <v>41.536</v>
+      </c>
+      <c r="G61">
+        <v>7.33</v>
+      </c>
+      <c r="H61">
+        <v>55.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>9.44</v>
+      </c>
+      <c r="K61">
+        <v>2.18</v>
+      </c>
+      <c r="L61">
+        <v>7.26</v>
+      </c>
+      <c r="M61">
+        <v>3.1110464</v>
+      </c>
+      <c r="N61">
+        <v>4.1489536</v>
+      </c>
+      <c r="O61">
+        <v>0.9127697920000001</v>
+      </c>
+      <c r="P61">
+        <v>3.236183808</v>
+      </c>
+      <c r="Q61">
+        <v>5.416183808</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1605379407804352</v>
+      </c>
+      <c r="T61">
+        <v>2.646476973487721</v>
+      </c>
+      <c r="U61">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V61">
+        <v>0.22</v>
+      </c>
+      <c r="W61">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>2.333619967866761</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1003595690702612</v>
+      </c>
+      <c r="C62">
+        <v>25.36606465730448</v>
+      </c>
+      <c r="D62">
+        <v>60.27606465730449</v>
+      </c>
+      <c r="E62">
+        <v>27.34</v>
+      </c>
+      <c r="F62">
+        <v>42.24</v>
+      </c>
+      <c r="G62">
+        <v>7.33</v>
+      </c>
+      <c r="H62">
+        <v>55.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>9.44</v>
+      </c>
+      <c r="K62">
+        <v>2.18</v>
+      </c>
+      <c r="L62">
+        <v>7.26</v>
+      </c>
+      <c r="M62">
+        <v>3.163776</v>
+      </c>
+      <c r="N62">
+        <v>4.096223999999999</v>
+      </c>
+      <c r="O62">
+        <v>0.9011692799999999</v>
+      </c>
+      <c r="P62">
+        <v>3.195054719999999</v>
+      </c>
+      <c r="Q62">
+        <v>5.37505472</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1632659226756529</v>
+      </c>
+      <c r="T62">
+        <v>2.705780927731586</v>
+      </c>
+      <c r="U62">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V62">
+        <v>0.22</v>
+      </c>
+      <c r="W62">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>2.294726301735647</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1004296024205439</v>
+      </c>
+      <c r="C63">
+        <v>24.59356941177288</v>
+      </c>
+      <c r="D63">
+        <v>60.20756941177288</v>
+      </c>
+      <c r="E63">
+        <v>28.044</v>
+      </c>
+      <c r="F63">
+        <v>42.944</v>
+      </c>
+      <c r="G63">
+        <v>7.33</v>
+      </c>
+      <c r="H63">
+        <v>55.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>9.44</v>
+      </c>
+      <c r="K63">
+        <v>2.18</v>
+      </c>
+      <c r="L63">
+        <v>7.26</v>
+      </c>
+      <c r="M63">
+        <v>3.2165056</v>
+      </c>
+      <c r="N63">
+        <v>4.0434944</v>
+      </c>
+      <c r="O63">
+        <v>0.8895687680000001</v>
+      </c>
+      <c r="P63">
+        <v>3.153925632</v>
+      </c>
+      <c r="Q63">
+        <v>5.333925632</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1661338010783177</v>
+      </c>
+      <c r="T63">
+        <v>2.768126110398212</v>
+      </c>
+      <c r="U63">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V63">
+        <v>0.22</v>
+      </c>
+      <c r="W63">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>2.257107837772768</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1004996357708267</v>
+      </c>
+      <c r="C64">
+        <v>23.82122965991518</v>
+      </c>
+      <c r="D64">
+        <v>60.13922965991519</v>
+      </c>
+      <c r="E64">
+        <v>28.748</v>
+      </c>
+      <c r="F64">
+        <v>43.648</v>
+      </c>
+      <c r="G64">
+        <v>7.33</v>
+      </c>
+      <c r="H64">
+        <v>55.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>9.44</v>
+      </c>
+      <c r="K64">
+        <v>2.18</v>
+      </c>
+      <c r="L64">
+        <v>7.26</v>
+      </c>
+      <c r="M64">
+        <v>3.2692352</v>
+      </c>
+      <c r="N64">
+        <v>3.9907648</v>
+      </c>
+      <c r="O64">
+        <v>0.8779682560000001</v>
+      </c>
+      <c r="P64">
+        <v>3.112796544</v>
+      </c>
+      <c r="Q64">
+        <v>5.292796544</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1691526204495439</v>
+      </c>
+      <c r="T64">
+        <v>2.833752618468345</v>
+      </c>
+      <c r="U64">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V64">
+        <v>0.22</v>
+      </c>
+      <c r="W64">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>2.220702872647401</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1005696691211094</v>
+      </c>
+      <c r="C65">
+        <v>23.04904487284357</v>
+      </c>
+      <c r="D65">
+        <v>60.07104487284357</v>
+      </c>
+      <c r="E65">
+        <v>29.45200000000001</v>
+      </c>
+      <c r="F65">
+        <v>44.352</v>
+      </c>
+      <c r="G65">
+        <v>7.33</v>
+      </c>
+      <c r="H65">
+        <v>55.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>9.44</v>
+      </c>
+      <c r="K65">
+        <v>2.18</v>
+      </c>
+      <c r="L65">
+        <v>7.26</v>
+      </c>
+      <c r="M65">
+        <v>3.3219648</v>
+      </c>
+      <c r="N65">
+        <v>3.9380352</v>
+      </c>
+      <c r="O65">
+        <v>0.8663677439999999</v>
+      </c>
+      <c r="P65">
+        <v>3.071667456</v>
+      </c>
+      <c r="Q65">
+        <v>5.251667456</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1723346192462417</v>
+      </c>
+      <c r="T65">
+        <v>2.90292650535308</v>
+      </c>
+      <c r="U65">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V65">
+        <v>0.22</v>
+      </c>
+      <c r="W65">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>2.185453620700617</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1006397024713922</v>
+      </c>
+      <c r="C66">
+        <v>22.27701452406597</v>
+      </c>
+      <c r="D66">
+        <v>60.00301452406597</v>
+      </c>
+      <c r="E66">
+        <v>30.15600000000001</v>
+      </c>
+      <c r="F66">
+        <v>45.056</v>
+      </c>
+      <c r="G66">
+        <v>7.33</v>
+      </c>
+      <c r="H66">
+        <v>55.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>9.44</v>
+      </c>
+      <c r="K66">
+        <v>2.18</v>
+      </c>
+      <c r="L66">
+        <v>7.26</v>
+      </c>
+      <c r="M66">
+        <v>3.3746944</v>
+      </c>
+      <c r="N66">
+        <v>3.8853056</v>
+      </c>
+      <c r="O66">
+        <v>0.8547672319999999</v>
+      </c>
+      <c r="P66">
+        <v>3.030538368</v>
+      </c>
+      <c r="Q66">
+        <v>5.210538368</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1756933957538671</v>
+      </c>
+      <c r="T66">
+        <v>2.975943385953634</v>
+      </c>
+      <c r="U66">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V66">
+        <v>0.22</v>
+      </c>
+      <c r="W66">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>2.15130590787717</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1007097358216749</v>
+      </c>
+      <c r="C67">
+        <v>21.50513808947274</v>
+      </c>
+      <c r="D67">
+        <v>59.93513808947274</v>
+      </c>
+      <c r="E67">
+        <v>30.86000000000001</v>
+      </c>
+      <c r="F67">
+        <v>45.76000000000001</v>
+      </c>
+      <c r="G67">
+        <v>7.33</v>
+      </c>
+      <c r="H67">
+        <v>55.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>9.44</v>
+      </c>
+      <c r="K67">
+        <v>2.18</v>
+      </c>
+      <c r="L67">
+        <v>7.26</v>
+      </c>
+      <c r="M67">
+        <v>3.427424</v>
+      </c>
+      <c r="N67">
+        <v>3.832576</v>
+      </c>
+      <c r="O67">
+        <v>0.8431667199999999</v>
+      </c>
+      <c r="P67">
+        <v>2.989409279999999</v>
+      </c>
+      <c r="Q67">
+        <v>5.169409279999999</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1792441023476426</v>
+      </c>
+      <c r="T67">
+        <v>3.053132659731362</v>
+      </c>
+      <c r="U67">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V67">
+        <v>0.22</v>
+      </c>
+      <c r="W67">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>2.118208893909828</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1007797691719577</v>
+      </c>
+      <c r="C68">
+        <v>20.73341504732297</v>
+      </c>
+      <c r="D68">
+        <v>59.86741504732297</v>
+      </c>
+      <c r="E68">
+        <v>31.56400000000001</v>
+      </c>
+      <c r="F68">
+        <v>46.46400000000001</v>
+      </c>
+      <c r="G68">
+        <v>7.33</v>
+      </c>
+      <c r="H68">
+        <v>55.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>9.44</v>
+      </c>
+      <c r="K68">
+        <v>2.18</v>
+      </c>
+      <c r="L68">
+        <v>7.26</v>
+      </c>
+      <c r="M68">
+        <v>3.4801536</v>
+      </c>
+      <c r="N68">
+        <v>3.7798464</v>
+      </c>
+      <c r="O68">
+        <v>0.8315662079999999</v>
+      </c>
+      <c r="P68">
+        <v>2.948280192</v>
+      </c>
+      <c r="Q68">
+        <v>5.128280192</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1830036740351697</v>
+      </c>
+      <c r="T68">
+        <v>3.134862479025427</v>
+      </c>
+      <c r="U68">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V68">
+        <v>0.22</v>
+      </c>
+      <c r="W68">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>2.086114819759679</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1008498025222404</v>
+      </c>
+      <c r="C69">
+        <v>19.96184487823133</v>
+      </c>
+      <c r="D69">
+        <v>59.79984487823133</v>
+      </c>
+      <c r="E69">
+        <v>32.26800000000001</v>
+      </c>
+      <c r="F69">
+        <v>47.16800000000001</v>
+      </c>
+      <c r="G69">
+        <v>7.33</v>
+      </c>
+      <c r="H69">
+        <v>55.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>9.44</v>
+      </c>
+      <c r="K69">
+        <v>2.18</v>
+      </c>
+      <c r="L69">
+        <v>7.26</v>
+      </c>
+      <c r="M69">
+        <v>3.5328832</v>
+      </c>
+      <c r="N69">
+        <v>3.7271168</v>
+      </c>
+      <c r="O69">
+        <v>0.8199656959999999</v>
+      </c>
+      <c r="P69">
+        <v>2.907151104</v>
+      </c>
+      <c r="Q69">
+        <v>5.087151103999999</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1869910985522437</v>
+      </c>
+      <c r="T69">
+        <v>3.22154562070095</v>
+      </c>
+      <c r="U69">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V69">
+        <v>0.22</v>
+      </c>
+      <c r="W69">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>2.054978777673714</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1009198358725232</v>
+      </c>
+      <c r="C70">
+        <v>19.1904270651546</v>
+      </c>
+      <c r="D70">
+        <v>59.7324270651546</v>
+      </c>
+      <c r="E70">
+        <v>32.97200000000001</v>
+      </c>
+      <c r="F70">
+        <v>47.87200000000001</v>
+      </c>
+      <c r="G70">
+        <v>7.33</v>
+      </c>
+      <c r="H70">
+        <v>55.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>9.44</v>
+      </c>
+      <c r="K70">
+        <v>2.18</v>
+      </c>
+      <c r="L70">
+        <v>7.26</v>
+      </c>
+      <c r="M70">
+        <v>3.5856128</v>
+      </c>
+      <c r="N70">
+        <v>3.6743872</v>
+      </c>
+      <c r="O70">
+        <v>0.8083651839999999</v>
+      </c>
+      <c r="P70">
+        <v>2.866022016</v>
+      </c>
+      <c r="Q70">
+        <v>5.046022015999999</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1912277371016349</v>
+      </c>
+      <c r="T70">
+        <v>3.313646458731194</v>
+      </c>
+      <c r="U70">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V70">
+        <v>0.22</v>
+      </c>
+      <c r="W70">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>2.024758501531454</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1097625292228059</v>
+      </c>
+      <c r="C71">
+        <v>11.04312506633658</v>
+      </c>
+      <c r="D71">
+        <v>52.28912506633659</v>
+      </c>
+      <c r="E71">
+        <v>33.67600000000001</v>
+      </c>
+      <c r="F71">
+        <v>48.57600000000001</v>
+      </c>
+      <c r="G71">
+        <v>7.33</v>
+      </c>
+      <c r="H71">
+        <v>55.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>9.44</v>
+      </c>
+      <c r="K71">
+        <v>2.18</v>
+      </c>
+      <c r="L71">
+        <v>7.26</v>
+      </c>
+      <c r="M71">
+        <v>4.430131200000001</v>
+      </c>
+      <c r="N71">
+        <v>2.829868799999999</v>
+      </c>
+      <c r="O71">
+        <v>0.6225711359999998</v>
+      </c>
+      <c r="P71">
+        <v>2.207297663999999</v>
+      </c>
+      <c r="Q71">
+        <v>4.387297663999998</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1957377071703417</v>
+      </c>
+      <c r="T71">
+        <v>3.411689286311776</v>
+      </c>
+      <c r="U71">
+        <v>0.0912</v>
+      </c>
+      <c r="V71">
+        <v>0.22</v>
+      </c>
+      <c r="W71">
+        <v>0.071136</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>1.63877765064836</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1099597025730887</v>
+      </c>
+      <c r="C72">
+        <v>10.19423938525755</v>
+      </c>
+      <c r="D72">
+        <v>52.14423938525756</v>
+      </c>
+      <c r="E72">
+        <v>34.38000000000001</v>
+      </c>
+      <c r="F72">
+        <v>49.28000000000001</v>
+      </c>
+      <c r="G72">
+        <v>7.33</v>
+      </c>
+      <c r="H72">
+        <v>55.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>9.44</v>
+      </c>
+      <c r="K72">
+        <v>2.18</v>
+      </c>
+      <c r="L72">
+        <v>7.26</v>
+      </c>
+      <c r="M72">
+        <v>4.494336000000001</v>
+      </c>
+      <c r="N72">
+        <v>2.765663999999999</v>
+      </c>
+      <c r="O72">
+        <v>0.6084460799999999</v>
+      </c>
+      <c r="P72">
+        <v>2.157217919999999</v>
+      </c>
+      <c r="Q72">
+        <v>4.337217919999999</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2005483419102956</v>
+      </c>
+      <c r="T72">
+        <v>3.516268302397729</v>
+      </c>
+      <c r="U72">
+        <v>0.0912</v>
+      </c>
+      <c r="V72">
+        <v>0.22</v>
+      </c>
+      <c r="W72">
+        <v>0.071136</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>1.615366541353383</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1101568759233714</v>
+      </c>
+      <c r="C73">
+        <v>9.34615440053124</v>
+      </c>
+      <c r="D73">
+        <v>52.00015440053124</v>
+      </c>
+      <c r="E73">
+        <v>35.084</v>
+      </c>
+      <c r="F73">
+        <v>49.984</v>
+      </c>
+      <c r="G73">
+        <v>7.33</v>
+      </c>
+      <c r="H73">
+        <v>55.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>9.44</v>
+      </c>
+      <c r="K73">
+        <v>2.18</v>
+      </c>
+      <c r="L73">
+        <v>7.26</v>
+      </c>
+      <c r="M73">
+        <v>4.5585408</v>
+      </c>
+      <c r="N73">
+        <v>2.7014592</v>
+      </c>
+      <c r="O73">
+        <v>0.5943210239999999</v>
+      </c>
+      <c r="P73">
+        <v>2.107138175999999</v>
+      </c>
+      <c r="Q73">
+        <v>4.287138175999999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2056907445633497</v>
+      </c>
+      <c r="T73">
+        <v>3.628059664420645</v>
+      </c>
+      <c r="U73">
+        <v>0.0912</v>
+      </c>
+      <c r="V73">
+        <v>0.22</v>
+      </c>
+      <c r="W73">
+        <v>0.071136</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>1.592614899925871</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1103540492736542</v>
+      </c>
+      <c r="C74">
+        <v>8.498863492994175</v>
+      </c>
+      <c r="D74">
+        <v>51.85686349299418</v>
+      </c>
+      <c r="E74">
+        <v>35.788</v>
+      </c>
+      <c r="F74">
+        <v>50.688</v>
+      </c>
+      <c r="G74">
+        <v>7.33</v>
+      </c>
+      <c r="H74">
+        <v>55.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>9.44</v>
+      </c>
+      <c r="K74">
+        <v>2.18</v>
+      </c>
+      <c r="L74">
+        <v>7.26</v>
+      </c>
+      <c r="M74">
+        <v>4.6227456</v>
+      </c>
+      <c r="N74">
+        <v>2.6372544</v>
+      </c>
+      <c r="O74">
+        <v>0.580195968</v>
+      </c>
+      <c r="P74">
+        <v>2.057058432</v>
+      </c>
+      <c r="Q74">
+        <v>4.237058432</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.211200461691622</v>
+      </c>
+      <c r="T74">
+        <v>3.747836123730913</v>
+      </c>
+      <c r="U74">
+        <v>0.0912</v>
+      </c>
+      <c r="V74">
+        <v>0.22</v>
+      </c>
+      <c r="W74">
+        <v>0.071136</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>1.570495248538012</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1105512226239369</v>
+      </c>
+      <c r="C75">
+        <v>7.652360116241162</v>
+      </c>
+      <c r="D75">
+        <v>51.71436011624117</v>
+      </c>
+      <c r="E75">
+        <v>36.492</v>
+      </c>
+      <c r="F75">
+        <v>51.392</v>
+      </c>
+      <c r="G75">
+        <v>7.33</v>
+      </c>
+      <c r="H75">
+        <v>55.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>9.44</v>
+      </c>
+      <c r="K75">
+        <v>2.18</v>
+      </c>
+      <c r="L75">
+        <v>7.26</v>
+      </c>
+      <c r="M75">
+        <v>4.686950400000001</v>
+      </c>
+      <c r="N75">
+        <v>2.573049599999999</v>
+      </c>
+      <c r="O75">
+        <v>0.5660709119999998</v>
+      </c>
+      <c r="P75">
+        <v>2.006978687999999</v>
+      </c>
+      <c r="Q75">
+        <v>4.186978687999999</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2171183060145811</v>
+      </c>
+      <c r="T75">
+        <v>3.876484913360459</v>
+      </c>
+      <c r="U75">
+        <v>0.0912</v>
+      </c>
+      <c r="V75">
+        <v>0.22</v>
+      </c>
+      <c r="W75">
+        <v>0.071136</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>1.548981614996395</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1107483959742196</v>
+      </c>
+      <c r="C76">
+        <v>6.806637795628184</v>
+      </c>
+      <c r="D76">
+        <v>51.57263779562819</v>
+      </c>
+      <c r="E76">
+        <v>37.19600000000001</v>
+      </c>
+      <c r="F76">
+        <v>52.096</v>
+      </c>
+      <c r="G76">
+        <v>7.33</v>
+      </c>
+      <c r="H76">
+        <v>55.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>9.44</v>
+      </c>
+      <c r="K76">
+        <v>2.18</v>
+      </c>
+      <c r="L76">
+        <v>7.26</v>
+      </c>
+      <c r="M76">
+        <v>4.7511552</v>
+      </c>
+      <c r="N76">
+        <v>2.508844799999999</v>
+      </c>
+      <c r="O76">
+        <v>0.5519458559999999</v>
+      </c>
+      <c r="P76">
+        <v>1.956898944</v>
+      </c>
+      <c r="Q76">
+        <v>4.136898943999999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.223491369131614</v>
+      </c>
+      <c r="T76">
+        <v>4.015029763730739</v>
+      </c>
+      <c r="U76">
+        <v>0.0912</v>
+      </c>
+      <c r="V76">
+        <v>0.22</v>
+      </c>
+      <c r="W76">
+        <v>0.071136</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>1.528049431009957</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1109455693245024</v>
+      </c>
+      <c r="C77">
+        <v>5.961690127291902</v>
+      </c>
+      <c r="D77">
+        <v>51.43169012729191</v>
+      </c>
+      <c r="E77">
+        <v>37.90000000000001</v>
+      </c>
+      <c r="F77">
+        <v>52.8</v>
+      </c>
+      <c r="G77">
+        <v>7.33</v>
+      </c>
+      <c r="H77">
+        <v>55.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>9.44</v>
+      </c>
+      <c r="K77">
+        <v>2.18</v>
+      </c>
+      <c r="L77">
+        <v>7.26</v>
+      </c>
+      <c r="M77">
+        <v>4.815360000000001</v>
+      </c>
+      <c r="N77">
+        <v>2.444639999999999</v>
+      </c>
+      <c r="O77">
+        <v>0.5378207999999998</v>
+      </c>
+      <c r="P77">
+        <v>1.906819199999999</v>
+      </c>
+      <c r="Q77">
+        <v>4.086819199999999</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2303742772980096</v>
+      </c>
+      <c r="T77">
+        <v>4.164658202130643</v>
+      </c>
+      <c r="U77">
+        <v>0.0912</v>
+      </c>
+      <c r="V77">
+        <v>0.22</v>
+      </c>
+      <c r="W77">
+        <v>0.071136</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>1.507675438596491</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1546883629114754</v>
+      </c>
+      <c r="C78">
+        <v>-14.15552573447528</v>
+      </c>
+      <c r="D78">
+        <v>32.01847426552472</v>
+      </c>
+      <c r="E78">
+        <v>38.60400000000001</v>
+      </c>
+      <c r="F78">
+        <v>53.504</v>
+      </c>
+      <c r="G78">
+        <v>7.33</v>
+      </c>
+      <c r="H78">
+        <v>55.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>9.44</v>
+      </c>
+      <c r="K78">
+        <v>2.18</v>
+      </c>
+      <c r="L78">
+        <v>7.26</v>
+      </c>
+      <c r="M78">
+        <v>8.378726400000001</v>
+      </c>
+      <c r="N78">
+        <v>-1.118726400000002</v>
+      </c>
+      <c r="O78">
+        <v>-0.2461198080000004</v>
+      </c>
+      <c r="P78">
+        <v>-0.8726065920000013</v>
+      </c>
+      <c r="Q78">
+        <v>1.307393407999998</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2431660954644806</v>
+      </c>
+      <c r="T78">
+        <v>4.442741205749579</v>
+      </c>
+      <c r="U78">
+        <v>0.1566</v>
+      </c>
+      <c r="V78">
+        <v>0.1906256301673724</v>
+      </c>
+      <c r="W78">
+        <v>0.1267480263157895</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.8664801371244201</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1558663629114754</v>
+      </c>
+      <c r="C79">
+        <v>-15.18171702620705</v>
+      </c>
+      <c r="D79">
+        <v>31.69628297379295</v>
+      </c>
+      <c r="E79">
+        <v>39.30800000000001</v>
+      </c>
+      <c r="F79">
+        <v>54.20800000000001</v>
+      </c>
+      <c r="G79">
+        <v>7.33</v>
+      </c>
+      <c r="H79">
+        <v>55.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>9.44</v>
+      </c>
+      <c r="K79">
+        <v>2.18</v>
+      </c>
+      <c r="L79">
+        <v>7.26</v>
+      </c>
+      <c r="M79">
+        <v>8.488972800000003</v>
+      </c>
+      <c r="N79">
+        <v>-1.228972800000003</v>
+      </c>
+      <c r="O79">
+        <v>-0.2703740160000006</v>
+      </c>
+      <c r="P79">
+        <v>-0.9585987840000023</v>
+      </c>
+      <c r="Q79">
+        <v>1.221401215999997</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2520515778759798</v>
+      </c>
+      <c r="T79">
+        <v>4.635903866869126</v>
+      </c>
+      <c r="U79">
+        <v>0.1566</v>
+      </c>
+      <c r="V79">
+        <v>0.1881499726327312</v>
+      </c>
+      <c r="W79">
+        <v>0.1271357142857143</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.8552271483305963</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1570443629114753</v>
+      </c>
+      <c r="C80">
+        <v>-16.20148870803413</v>
+      </c>
+      <c r="D80">
+        <v>31.38051129196588</v>
+      </c>
+      <c r="E80">
+        <v>40.01200000000001</v>
+      </c>
+      <c r="F80">
+        <v>54.91200000000001</v>
+      </c>
+      <c r="G80">
+        <v>7.33</v>
+      </c>
+      <c r="H80">
+        <v>55.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>9.44</v>
+      </c>
+      <c r="K80">
+        <v>2.18</v>
+      </c>
+      <c r="L80">
+        <v>7.26</v>
+      </c>
+      <c r="M80">
+        <v>8.599219200000002</v>
+      </c>
+      <c r="N80">
+        <v>-1.339219200000002</v>
+      </c>
+      <c r="O80">
+        <v>-0.2946282240000005</v>
+      </c>
+      <c r="P80">
+        <v>-1.044590976000002</v>
+      </c>
+      <c r="Q80">
+        <v>1.135409023999998</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.261744831415797</v>
+      </c>
+      <c r="T80">
+        <v>4.846626769908631</v>
+      </c>
+      <c r="U80">
+        <v>0.1566</v>
+      </c>
+      <c r="V80">
+        <v>0.1857377934964141</v>
+      </c>
+      <c r="W80">
+        <v>0.1275134615384615</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.8442626977109733</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1582223629114754</v>
+      </c>
+      <c r="C81">
+        <v>-17.21503075192534</v>
+      </c>
+      <c r="D81">
+        <v>31.07096924807466</v>
+      </c>
+      <c r="E81">
+        <v>40.71600000000001</v>
+      </c>
+      <c r="F81">
+        <v>55.61600000000001</v>
+      </c>
+      <c r="G81">
+        <v>7.33</v>
+      </c>
+      <c r="H81">
+        <v>55.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>9.44</v>
+      </c>
+      <c r="K81">
+        <v>2.18</v>
+      </c>
+      <c r="L81">
+        <v>7.26</v>
+      </c>
+      <c r="M81">
+        <v>8.709465600000001</v>
+      </c>
+      <c r="N81">
+        <v>-1.449465600000002</v>
+      </c>
+      <c r="O81">
+        <v>-0.3188824320000004</v>
+      </c>
+      <c r="P81">
+        <v>-1.130583168000001</v>
+      </c>
+      <c r="Q81">
+        <v>1.049416831999998</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2723612519594065</v>
+      </c>
+      <c r="T81">
+        <v>5.077418520856662</v>
+      </c>
+      <c r="U81">
+        <v>0.1566</v>
+      </c>
+      <c r="V81">
+        <v>0.1833866821863329</v>
+      </c>
+      <c r="W81">
+        <v>0.1278816455696203</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.8335758281196952</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1594003629114754</v>
+      </c>
+      <c r="C82">
+        <v>-18.22252570741813</v>
+      </c>
+      <c r="D82">
+        <v>30.76747429258188</v>
+      </c>
+      <c r="E82">
+        <v>41.42000000000001</v>
+      </c>
+      <c r="F82">
+        <v>56.32000000000001</v>
+      </c>
+      <c r="G82">
+        <v>7.33</v>
+      </c>
+      <c r="H82">
+        <v>55.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>9.44</v>
+      </c>
+      <c r="K82">
+        <v>2.18</v>
+      </c>
+      <c r="L82">
+        <v>7.26</v>
+      </c>
+      <c r="M82">
+        <v>8.819712000000003</v>
+      </c>
+      <c r="N82">
+        <v>-1.559712000000003</v>
+      </c>
+      <c r="O82">
+        <v>-0.3431366400000007</v>
+      </c>
+      <c r="P82">
+        <v>-1.216575360000002</v>
+      </c>
+      <c r="Q82">
+        <v>0.9634246399999975</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2840393145573767</v>
+      </c>
+      <c r="T82">
+        <v>5.331289446899495</v>
+      </c>
+      <c r="U82">
+        <v>0.1566</v>
+      </c>
+      <c r="V82">
+        <v>0.1810943486590038</v>
+      </c>
+      <c r="W82">
+        <v>0.128240625</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.8231561302681989</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1605783629114754</v>
+      </c>
+      <c r="C83">
+        <v>-19.22414906061601</v>
+      </c>
+      <c r="D83">
+        <v>30.469850939384</v>
+      </c>
+      <c r="E83">
+        <v>42.12400000000001</v>
+      </c>
+      <c r="F83">
+        <v>57.02400000000001</v>
+      </c>
+      <c r="G83">
+        <v>7.33</v>
+      </c>
+      <c r="H83">
+        <v>55.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>9.44</v>
+      </c>
+      <c r="K83">
+        <v>2.18</v>
+      </c>
+      <c r="L83">
+        <v>7.26</v>
+      </c>
+      <c r="M83">
+        <v>8.929958400000002</v>
+      </c>
+      <c r="N83">
+        <v>-1.669958400000002</v>
+      </c>
+      <c r="O83">
+        <v>-0.3673908480000005</v>
+      </c>
+      <c r="P83">
+        <v>-1.302567552000002</v>
+      </c>
+      <c r="Q83">
+        <v>0.877432447999998</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2969466469025019</v>
+      </c>
+      <c r="T83">
+        <v>5.611883628315258</v>
+      </c>
+      <c r="U83">
+        <v>0.1566</v>
+      </c>
+      <c r="V83">
+        <v>0.1788586159595099</v>
+      </c>
+      <c r="W83">
+        <v>0.1285907407407408</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.8129937089068633</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1617563629114754</v>
+      </c>
+      <c r="C84">
+        <v>-20.22006957254947</v>
+      </c>
+      <c r="D84">
+        <v>30.17793042745054</v>
+      </c>
+      <c r="E84">
+        <v>42.82800000000001</v>
+      </c>
+      <c r="F84">
+        <v>57.72800000000001</v>
+      </c>
+      <c r="G84">
+        <v>7.33</v>
+      </c>
+      <c r="H84">
+        <v>55.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>9.44</v>
+      </c>
+      <c r="K84">
+        <v>2.18</v>
+      </c>
+      <c r="L84">
+        <v>7.26</v>
+      </c>
+      <c r="M84">
+        <v>9.040204800000001</v>
+      </c>
+      <c r="N84">
+        <v>-1.780204800000002</v>
+      </c>
+      <c r="O84">
+        <v>-0.3916450560000004</v>
+      </c>
+      <c r="P84">
+        <v>-1.388559744000001</v>
+      </c>
+      <c r="Q84">
+        <v>0.7914402559999985</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3112881272859743</v>
+      </c>
+      <c r="T84">
+        <v>5.92365494099944</v>
+      </c>
+      <c r="U84">
+        <v>0.1566</v>
+      </c>
+      <c r="V84">
+        <v>0.1766774133258574</v>
+      </c>
+      <c r="W84">
+        <v>0.1289323170731707</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.8030791514811698</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2083377891969306</v>
+      </c>
+      <c r="C85">
+        <v>-29.21561948783724</v>
+      </c>
+      <c r="D85">
+        <v>21.88638051216277</v>
+      </c>
+      <c r="E85">
+        <v>43.53200000000001</v>
+      </c>
+      <c r="F85">
+        <v>58.43200000000001</v>
+      </c>
+      <c r="G85">
+        <v>7.33</v>
+      </c>
+      <c r="H85">
+        <v>55.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>9.44</v>
+      </c>
+      <c r="K85">
+        <v>2.18</v>
+      </c>
+      <c r="L85">
+        <v>7.26</v>
+      </c>
+      <c r="M85">
+        <v>12.2006016</v>
+      </c>
+      <c r="N85">
+        <v>-4.940601600000003</v>
+      </c>
+      <c r="O85">
+        <v>-1.086932352</v>
+      </c>
+      <c r="P85">
+        <v>-3.853669248000002</v>
+      </c>
+      <c r="Q85">
+        <v>-1.673669248000002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3395369952760623</v>
+      </c>
+      <c r="T85">
+        <v>6.537760766870921</v>
+      </c>
+      <c r="U85">
+        <v>0.2088</v>
+      </c>
+      <c r="V85">
+        <v>0.1309115773438582</v>
+      </c>
+      <c r="W85">
+        <v>0.1814656626506024</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.5950526242902644</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2100377891969306</v>
+      </c>
+      <c r="C86">
+        <v>-30.13690123998533</v>
+      </c>
+      <c r="D86">
+        <v>21.66909876001467</v>
+      </c>
+      <c r="E86">
+        <v>44.236</v>
+      </c>
+      <c r="F86">
+        <v>59.136</v>
+      </c>
+      <c r="G86">
+        <v>7.33</v>
+      </c>
+      <c r="H86">
+        <v>55.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>9.44</v>
+      </c>
+      <c r="K86">
+        <v>2.18</v>
+      </c>
+      <c r="L86">
+        <v>7.26</v>
+      </c>
+      <c r="M86">
+        <v>12.3475968</v>
+      </c>
+      <c r="N86">
+        <v>-5.087596800000002</v>
+      </c>
+      <c r="O86">
+        <v>-1.119271296</v>
+      </c>
+      <c r="P86">
+        <v>-3.968325504000001</v>
+      </c>
+      <c r="Q86">
+        <v>-1.788325504000002</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3583330574808161</v>
+      </c>
+      <c r="T86">
+        <v>6.946370814800349</v>
+      </c>
+      <c r="U86">
+        <v>0.2088</v>
+      </c>
+      <c r="V86">
+        <v>0.1293531061850027</v>
+      </c>
+      <c r="W86">
+        <v>0.1817910714285715</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.587968664477285</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2117377891969306</v>
+      </c>
+      <c r="C87">
+        <v>-31.05391117877943</v>
+      </c>
+      <c r="D87">
+        <v>21.45608882122058</v>
+      </c>
+      <c r="E87">
+        <v>44.94</v>
+      </c>
+      <c r="F87">
+        <v>59.84</v>
+      </c>
+      <c r="G87">
+        <v>7.33</v>
+      </c>
+      <c r="H87">
+        <v>55.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>9.44</v>
+      </c>
+      <c r="K87">
+        <v>2.18</v>
+      </c>
+      <c r="L87">
+        <v>7.26</v>
+      </c>
+      <c r="M87">
+        <v>12.494592</v>
+      </c>
+      <c r="N87">
+        <v>-5.234592000000001</v>
+      </c>
+      <c r="O87">
+        <v>-1.15161024</v>
+      </c>
+      <c r="P87">
+        <v>-4.082981760000001</v>
+      </c>
+      <c r="Q87">
+        <v>-1.902981760000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3796352613128705</v>
+      </c>
+      <c r="T87">
+        <v>7.409462202453707</v>
+      </c>
+      <c r="U87">
+        <v>0.2088</v>
+      </c>
+      <c r="V87">
+        <v>0.1278313049357674</v>
+      </c>
+      <c r="W87">
+        <v>0.1821088235294118</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.58105138607167</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2134377891969306</v>
+      </c>
+      <c r="C88">
+        <v>-31.96677405527257</v>
+      </c>
+      <c r="D88">
+        <v>21.24722594472743</v>
+      </c>
+      <c r="E88">
+        <v>45.64400000000001</v>
+      </c>
+      <c r="F88">
+        <v>60.544</v>
+      </c>
+      <c r="G88">
+        <v>7.33</v>
+      </c>
+      <c r="H88">
+        <v>55.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>9.44</v>
+      </c>
+      <c r="K88">
+        <v>2.18</v>
+      </c>
+      <c r="L88">
+        <v>7.26</v>
+      </c>
+      <c r="M88">
+        <v>12.6415872</v>
+      </c>
+      <c r="N88">
+        <v>-5.381587200000002</v>
+      </c>
+      <c r="O88">
+        <v>-1.183949184</v>
+      </c>
+      <c r="P88">
+        <v>-4.197638016000002</v>
+      </c>
+      <c r="Q88">
+        <v>-2.017638016000002</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4039806371209326</v>
+      </c>
+      <c r="T88">
+        <v>7.938709502628971</v>
+      </c>
+      <c r="U88">
+        <v>0.2088</v>
+      </c>
+      <c r="V88">
+        <v>0.1263448944132585</v>
+      </c>
+      <c r="W88">
+        <v>0.1824191860465116</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.5742949746057203</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2151377891969306</v>
+      </c>
+      <c r="C89">
+        <v>-32.87560980982374</v>
+      </c>
+      <c r="D89">
+        <v>21.04239019017627</v>
+      </c>
+      <c r="E89">
+        <v>46.34800000000001</v>
+      </c>
+      <c r="F89">
+        <v>61.248</v>
+      </c>
+      <c r="G89">
+        <v>7.33</v>
+      </c>
+      <c r="H89">
+        <v>55.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>9.44</v>
+      </c>
+      <c r="K89">
+        <v>2.18</v>
+      </c>
+      <c r="L89">
+        <v>7.26</v>
+      </c>
+      <c r="M89">
+        <v>12.7885824</v>
+      </c>
+      <c r="N89">
+        <v>-5.528582400000001</v>
+      </c>
+      <c r="O89">
+        <v>-1.216288128</v>
+      </c>
+      <c r="P89">
+        <v>-4.312294272000001</v>
+      </c>
+      <c r="Q89">
+        <v>-2.132294272000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4320714553610045</v>
+      </c>
+      <c r="T89">
+        <v>8.549379464369663</v>
+      </c>
+      <c r="U89">
+        <v>0.2088</v>
+      </c>
+      <c r="V89">
+        <v>0.1248926542475888</v>
+      </c>
+      <c r="W89">
+        <v>0.1827224137931035</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.5676938829435856</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2168377891969306</v>
+      </c>
+      <c r="C90">
+        <v>-33.78053380177317</v>
+      </c>
+      <c r="D90">
+        <v>20.84146619822683</v>
+      </c>
+      <c r="E90">
+        <v>47.05200000000001</v>
+      </c>
+      <c r="F90">
+        <v>61.95200000000001</v>
+      </c>
+      <c r="G90">
+        <v>7.33</v>
+      </c>
+      <c r="H90">
+        <v>55.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>9.44</v>
+      </c>
+      <c r="K90">
+        <v>2.18</v>
+      </c>
+      <c r="L90">
+        <v>7.26</v>
+      </c>
+      <c r="M90">
+        <v>12.9355776</v>
+      </c>
+      <c r="N90">
+        <v>-5.675577600000002</v>
+      </c>
+      <c r="O90">
+        <v>-1.248627072000001</v>
+      </c>
+      <c r="P90">
+        <v>-4.426950528000002</v>
+      </c>
+      <c r="Q90">
+        <v>-2.246950528000002</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4648440766410882</v>
+      </c>
+      <c r="T90">
+        <v>9.261827753067136</v>
+      </c>
+      <c r="U90">
+        <v>0.2088</v>
+      </c>
+      <c r="V90">
+        <v>0.1234734195402299</v>
+      </c>
+      <c r="W90">
+        <v>0.18301875</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.5612428160919539</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2185377891969306</v>
+      </c>
+      <c r="C91">
+        <v>-34.68165702608393</v>
+      </c>
+      <c r="D91">
+        <v>20.64434297391608</v>
+      </c>
+      <c r="E91">
+        <v>47.75600000000001</v>
+      </c>
+      <c r="F91">
+        <v>62.65600000000001</v>
+      </c>
+      <c r="G91">
+        <v>7.33</v>
+      </c>
+      <c r="H91">
+        <v>55.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>9.44</v>
+      </c>
+      <c r="K91">
+        <v>2.18</v>
+      </c>
+      <c r="L91">
+        <v>7.26</v>
+      </c>
+      <c r="M91">
+        <v>13.0825728</v>
+      </c>
+      <c r="N91">
+        <v>-5.822572800000001</v>
+      </c>
+      <c r="O91">
+        <v>-1.280966016</v>
+      </c>
+      <c r="P91">
+        <v>-4.541606784000001</v>
+      </c>
+      <c r="Q91">
+        <v>-2.361606784000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5035753563357326</v>
+      </c>
+      <c r="T91">
+        <v>10.10381209425506</v>
+      </c>
+      <c r="U91">
+        <v>0.2088</v>
+      </c>
+      <c r="V91">
+        <v>0.122086077747643</v>
+      </c>
+      <c r="W91">
+        <v>0.1833084269662922</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.554936717034741</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2202377891969306</v>
+      </c>
+      <c r="C92">
+        <v>-35.57908631780421</v>
+      </c>
+      <c r="D92">
+        <v>20.4509136821958</v>
+      </c>
+      <c r="E92">
+        <v>48.46000000000001</v>
+      </c>
+      <c r="F92">
+        <v>63.36000000000001</v>
+      </c>
+      <c r="G92">
+        <v>7.33</v>
+      </c>
+      <c r="H92">
+        <v>55.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>9.44</v>
+      </c>
+      <c r="K92">
+        <v>2.18</v>
+      </c>
+      <c r="L92">
+        <v>7.26</v>
+      </c>
+      <c r="M92">
+        <v>13.229568</v>
+      </c>
+      <c r="N92">
+        <v>-5.969568000000002</v>
+      </c>
+      <c r="O92">
+        <v>-1.313304960000001</v>
+      </c>
+      <c r="P92">
+        <v>-4.656263040000002</v>
+      </c>
+      <c r="Q92">
+        <v>-2.476263040000002</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5500528919693057</v>
+      </c>
+      <c r="T92">
+        <v>11.11419330368056</v>
+      </c>
+      <c r="U92">
+        <v>0.2088</v>
+      </c>
+      <c r="V92">
+        <v>0.1207295657726692</v>
+      </c>
+      <c r="W92">
+        <v>0.1835916666666667</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.5487707535121327</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2219377891969306</v>
+      </c>
+      <c r="C93">
+        <v>-36.47292454514215</v>
+      </c>
+      <c r="D93">
+        <v>20.26107545485786</v>
+      </c>
+      <c r="E93">
+        <v>49.16400000000001</v>
+      </c>
+      <c r="F93">
+        <v>64.06400000000001</v>
+      </c>
+      <c r="G93">
+        <v>7.33</v>
+      </c>
+      <c r="H93">
+        <v>55.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>9.44</v>
+      </c>
+      <c r="K93">
+        <v>2.18</v>
+      </c>
+      <c r="L93">
+        <v>7.26</v>
+      </c>
+      <c r="M93">
+        <v>13.3765632</v>
+      </c>
+      <c r="N93">
+        <v>-6.116563200000003</v>
+      </c>
+      <c r="O93">
+        <v>-1.345643904000001</v>
+      </c>
+      <c r="P93">
+        <v>-4.770919296000002</v>
+      </c>
+      <c r="Q93">
+        <v>-2.590919296000003</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6068587688547844</v>
+      </c>
+      <c r="T93">
+        <v>12.34910367075618</v>
+      </c>
+      <c r="U93">
+        <v>0.2088</v>
+      </c>
+      <c r="V93">
+        <v>0.1194028672476948</v>
+      </c>
+      <c r="W93">
+        <v>0.1838686813186813</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.54274030567134</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2236377891969306</v>
+      </c>
+      <c r="C94">
+        <v>-37.3632707918859</v>
+      </c>
+      <c r="D94">
+        <v>20.07472920811412</v>
+      </c>
+      <c r="E94">
+        <v>49.86800000000002</v>
+      </c>
+      <c r="F94">
+        <v>64.76800000000001</v>
+      </c>
+      <c r="G94">
+        <v>7.33</v>
+      </c>
+      <c r="H94">
+        <v>55.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>9.44</v>
+      </c>
+      <c r="K94">
+        <v>2.18</v>
+      </c>
+      <c r="L94">
+        <v>7.26</v>
+      </c>
+      <c r="M94">
+        <v>13.5235584</v>
+      </c>
+      <c r="N94">
+        <v>-6.263558400000004</v>
+      </c>
+      <c r="O94">
+        <v>-1.377982848000001</v>
+      </c>
+      <c r="P94">
+        <v>-4.885575552000003</v>
+      </c>
+      <c r="Q94">
+        <v>-2.705575552000004</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.6778661149616327</v>
+      </c>
+      <c r="T94">
+        <v>13.89274162960071</v>
+      </c>
+      <c r="U94">
+        <v>0.2088</v>
+      </c>
+      <c r="V94">
+        <v>0.1181050099950025</v>
+      </c>
+      <c r="W94">
+        <v>0.1841396739130435</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.5368409545227384</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2253377891969306</v>
+      </c>
+      <c r="C95">
+        <v>-38.25022052984899</v>
+      </c>
+      <c r="D95">
+        <v>19.89177947015102</v>
+      </c>
+      <c r="E95">
+        <v>50.57200000000001</v>
+      </c>
+      <c r="F95">
+        <v>65.47200000000001</v>
+      </c>
+      <c r="G95">
+        <v>7.33</v>
+      </c>
+      <c r="H95">
+        <v>55.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>9.44</v>
+      </c>
+      <c r="K95">
+        <v>2.18</v>
+      </c>
+      <c r="L95">
+        <v>7.26</v>
+      </c>
+      <c r="M95">
+        <v>13.6705536</v>
+      </c>
+      <c r="N95">
+        <v>-6.410553600000004</v>
+      </c>
+      <c r="O95">
+        <v>-1.410321792000001</v>
+      </c>
+      <c r="P95">
+        <v>-5.000231808000002</v>
+      </c>
+      <c r="Q95">
+        <v>-2.820231808000003</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.7691612742418659</v>
+      </c>
+      <c r="T95">
+        <v>15.87741900525796</v>
+      </c>
+      <c r="U95">
+        <v>0.2088</v>
+      </c>
+      <c r="V95">
+        <v>0.1168350636509702</v>
+      </c>
+      <c r="W95">
+        <v>0.1844048387096774</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.5310684711407736</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2270377891969306</v>
+      </c>
+      <c r="C96">
+        <v>-39.13386578197144</v>
+      </c>
+      <c r="D96">
+        <v>19.71213421802857</v>
+      </c>
+      <c r="E96">
+        <v>51.27600000000002</v>
+      </c>
+      <c r="F96">
+        <v>66.17600000000002</v>
+      </c>
+      <c r="G96">
+        <v>7.33</v>
+      </c>
+      <c r="H96">
+        <v>55.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>9.44</v>
+      </c>
+      <c r="K96">
+        <v>2.18</v>
+      </c>
+      <c r="L96">
+        <v>7.26</v>
+      </c>
+      <c r="M96">
+        <v>13.8175488</v>
+      </c>
+      <c r="N96">
+        <v>-6.557548800000005</v>
+      </c>
+      <c r="O96">
+        <v>-1.442660736000001</v>
+      </c>
+      <c r="P96">
+        <v>-5.114888064000004</v>
+      </c>
+      <c r="Q96">
+        <v>-2.934888064000004</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.8908881532821771</v>
+      </c>
+      <c r="T96">
+        <v>18.52365550613429</v>
+      </c>
+      <c r="U96">
+        <v>0.2088</v>
+      </c>
+      <c r="V96">
+        <v>0.1155921374419173</v>
+      </c>
+      <c r="W96">
+        <v>0.1846643617021277</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.5254188065541696</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2287377891969306</v>
+      </c>
+      <c r="C97">
+        <v>-40.01429527666197</v>
+      </c>
+      <c r="D97">
+        <v>19.53570472333804</v>
+      </c>
+      <c r="E97">
+        <v>51.98000000000001</v>
+      </c>
+      <c r="F97">
+        <v>66.88000000000001</v>
+      </c>
+      <c r="G97">
+        <v>7.33</v>
+      </c>
+      <c r="H97">
+        <v>55.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>9.44</v>
+      </c>
+      <c r="K97">
+        <v>2.18</v>
+      </c>
+      <c r="L97">
+        <v>7.26</v>
+      </c>
+      <c r="M97">
+        <v>13.964544</v>
+      </c>
+      <c r="N97">
+        <v>-6.704544000000004</v>
+      </c>
+      <c r="O97">
+        <v>-1.474999680000001</v>
+      </c>
+      <c r="P97">
+        <v>-5.229544320000003</v>
+      </c>
+      <c r="Q97">
+        <v>-3.049544320000003</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.061305783938613</v>
+      </c>
+      <c r="T97">
+        <v>22.22838660736115</v>
+      </c>
+      <c r="U97">
+        <v>0.2088</v>
+      </c>
+      <c r="V97">
+        <v>0.1143753781004234</v>
+      </c>
+      <c r="W97">
+        <v>0.1849184210526316</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.519888082274652</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2304377891969306</v>
+      </c>
+      <c r="C98">
+        <v>-40.89159459392525</v>
+      </c>
+      <c r="D98">
+        <v>19.36240540607475</v>
+      </c>
+      <c r="E98">
+        <v>52.684</v>
+      </c>
+      <c r="F98">
+        <v>67.584</v>
+      </c>
+      <c r="G98">
+        <v>7.33</v>
+      </c>
+      <c r="H98">
+        <v>55.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>9.44</v>
+      </c>
+      <c r="K98">
+        <v>2.18</v>
+      </c>
+      <c r="L98">
+        <v>7.26</v>
+      </c>
+      <c r="M98">
+        <v>14.1115392</v>
+      </c>
+      <c r="N98">
+        <v>-6.851539200000001</v>
+      </c>
+      <c r="O98">
+        <v>-1.507338624</v>
+      </c>
+      <c r="P98">
+        <v>-5.344200576000001</v>
+      </c>
+      <c r="Q98">
+        <v>-3.164200576000002</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.316932229923263</v>
+      </c>
+      <c r="T98">
+        <v>27.78548325920138</v>
+      </c>
+      <c r="U98">
+        <v>0.2088</v>
+      </c>
+      <c r="V98">
+        <v>0.1131839679118774</v>
+      </c>
+      <c r="W98">
+        <v>0.1851671875</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.5144725814176245</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2321377891969306</v>
+      </c>
+      <c r="C99">
+        <v>-41.76584630378005</v>
+      </c>
+      <c r="D99">
+        <v>19.19215369621994</v>
+      </c>
+      <c r="E99">
+        <v>53.388</v>
+      </c>
+      <c r="F99">
+        <v>68.288</v>
+      </c>
+      <c r="G99">
+        <v>7.33</v>
+      </c>
+      <c r="H99">
+        <v>55.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>9.44</v>
+      </c>
+      <c r="K99">
+        <v>2.18</v>
+      </c>
+      <c r="L99">
+        <v>7.26</v>
+      </c>
+      <c r="M99">
+        <v>14.2585344</v>
+      </c>
+      <c r="N99">
+        <v>-6.9985344</v>
+      </c>
+      <c r="O99">
+        <v>-1.539677568</v>
+      </c>
+      <c r="P99">
+        <v>-5.458856832</v>
+      </c>
+      <c r="Q99">
+        <v>-3.278856832000001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.742976306564351</v>
+      </c>
+      <c r="T99">
+        <v>37.04731101226851</v>
+      </c>
+      <c r="U99">
+        <v>0.2088</v>
+      </c>
+      <c r="V99">
+        <v>0.112017122881858</v>
+      </c>
+      <c r="W99">
+        <v>0.1854108247422681</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.5091687403720819</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2338377891969306</v>
+      </c>
+      <c r="C100">
+        <v>-42.63713009743829</v>
+      </c>
+      <c r="D100">
+        <v>19.02486990256172</v>
+      </c>
+      <c r="E100">
+        <v>54.09200000000001</v>
+      </c>
+      <c r="F100">
+        <v>68.992</v>
+      </c>
+      <c r="G100">
+        <v>7.33</v>
+      </c>
+      <c r="H100">
+        <v>55.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>9.44</v>
+      </c>
+      <c r="K100">
+        <v>2.18</v>
+      </c>
+      <c r="L100">
+        <v>7.26</v>
+      </c>
+      <c r="M100">
+        <v>14.4055296</v>
+      </c>
+      <c r="N100">
+        <v>-7.145529600000001</v>
+      </c>
+      <c r="O100">
+        <v>-1.572016512</v>
+      </c>
+      <c r="P100">
+        <v>-5.573513088000001</v>
+      </c>
+      <c r="Q100">
+        <v>-3.393513088000002</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.595064459846527</v>
+      </c>
+      <c r="T100">
+        <v>55.57096651840276</v>
+      </c>
+      <c r="U100">
+        <v>0.2088</v>
+      </c>
+      <c r="V100">
+        <v>0.1108740910157166</v>
+      </c>
+      <c r="W100">
+        <v>0.1856494897959184</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.5039731409805301</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2660207388020017</v>
+      </c>
+      <c r="C101">
+        <v>-46.03576278169651</v>
+      </c>
+      <c r="D101">
+        <v>16.33023721830348</v>
+      </c>
+      <c r="E101">
+        <v>54.796</v>
+      </c>
+      <c r="F101">
+        <v>69.696</v>
+      </c>
+      <c r="G101">
+        <v>7.33</v>
+      </c>
+      <c r="H101">
+        <v>55.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>9.44</v>
+      </c>
+      <c r="K101">
+        <v>2.18</v>
+      </c>
+      <c r="L101">
+        <v>7.26</v>
+      </c>
+      <c r="M101">
+        <v>16.6434048</v>
+      </c>
+      <c r="N101">
+        <v>-9.383404799999999</v>
+      </c>
+      <c r="O101">
+        <v>-2.064349056</v>
+      </c>
+      <c r="P101">
+        <v>-7.319055744</v>
+      </c>
+      <c r="Q101">
+        <v>-5.139055744</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.229623880200161</v>
+      </c>
+      <c r="T101">
+        <v>112.8439973956557</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.09596594081518706</v>
+      </c>
+      <c r="W101">
+        <v>0.2158833333333333</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.4362088218872139</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
